--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_food_processing.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_food_processing.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1223798583336566</v>
+        <v>0.1221047655899211</v>
       </c>
       <c r="C2">
-        <v>3335.806657897852</v>
+        <v>3321.332065298579</v>
       </c>
       <c r="D2">
-        <v>3314.506657897852</v>
+        <v>3326.456065298578</v>
       </c>
       <c r="E2">
-        <v>-2527</v>
+        <v>-2500.576</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.424</v>
       </c>
       <c r="G2">
         <v>21.3</v>
@@ -1445,28 +1445,28 @@
         <v>225.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3291272</v>
       </c>
       <c r="N2">
-        <v>225.6</v>
+        <v>224.2708728</v>
       </c>
       <c r="O2">
-        <v>56.91441016338471</v>
+        <v>56.57909770496223</v>
       </c>
       <c r="P2">
-        <v>168.6855898366153</v>
+        <v>167.6917750950378</v>
       </c>
       <c r="Q2">
-        <v>349.8855898366153</v>
+        <v>348.8917750950378</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1223798583336566</v>
+        <v>0.1229582449736656</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6204701967425962</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>169.7354474425021</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1221047655899211</v>
+        <v>0.1218296728461856</v>
       </c>
       <c r="C3">
-        <v>3321.332065298579</v>
+        <v>3306.943944076723</v>
       </c>
       <c r="D3">
-        <v>3326.456065298578</v>
+        <v>3338.491944076723</v>
       </c>
       <c r="E3">
-        <v>-2500.576</v>
+        <v>-2474.152</v>
       </c>
       <c r="F3">
-        <v>26.424</v>
+        <v>52.84800000000001</v>
       </c>
       <c r="G3">
         <v>21.3</v>
@@ -1527,28 +1527,28 @@
         <v>225.6</v>
       </c>
       <c r="M3">
-        <v>1.3291272</v>
+        <v>2.6582544</v>
       </c>
       <c r="N3">
-        <v>224.2708728</v>
+        <v>222.9417456</v>
       </c>
       <c r="O3">
-        <v>56.57909770496223</v>
+        <v>56.24378524653975</v>
       </c>
       <c r="P3">
-        <v>167.6917750950378</v>
+        <v>166.6979603534602</v>
       </c>
       <c r="Q3">
-        <v>348.8917750950378</v>
+        <v>347.8979603534602</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1229582449736656</v>
+        <v>0.1235484354226545</v>
       </c>
       <c r="T3">
-        <v>0.6204701967425962</v>
+        <v>0.6252162298350371</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>169.7354474425021</v>
+        <v>84.86772372125105</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1218296728461856</v>
+        <v>0.12155458010245</v>
       </c>
       <c r="C4">
-        <v>3306.943944076723</v>
+        <v>3292.643236260418</v>
       </c>
       <c r="D4">
-        <v>3338.491944076723</v>
+        <v>3350.615236260418</v>
       </c>
       <c r="E4">
-        <v>-2474.152</v>
+        <v>-2447.728</v>
       </c>
       <c r="F4">
-        <v>52.84800000000001</v>
+        <v>79.27200000000001</v>
       </c>
       <c r="G4">
         <v>21.3</v>
@@ -1609,28 +1609,28 @@
         <v>225.6</v>
       </c>
       <c r="M4">
-        <v>2.6582544</v>
+        <v>3.9873816</v>
       </c>
       <c r="N4">
-        <v>222.9417456</v>
+        <v>221.6126184</v>
       </c>
       <c r="O4">
-        <v>56.24378524653975</v>
+        <v>55.90847278811727</v>
       </c>
       <c r="P4">
-        <v>166.6979603534602</v>
+        <v>165.7041456118827</v>
       </c>
       <c r="Q4">
-        <v>347.8979603534602</v>
+        <v>346.9041456118828</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1235484354226545</v>
+        <v>0.1241507947468801</v>
       </c>
       <c r="T4">
-        <v>0.6252162298350371</v>
+        <v>0.6300601192798995</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.86772372125105</v>
+        <v>56.57848248083404</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.12155458010245</v>
+        <v>0.1212794873587145</v>
       </c>
       <c r="C5">
-        <v>3292.643236260418</v>
+        <v>3278.430897611064</v>
       </c>
       <c r="D5">
-        <v>3350.615236260418</v>
+        <v>3362.826897611063</v>
       </c>
       <c r="E5">
-        <v>-2447.728</v>
+        <v>-2421.304</v>
       </c>
       <c r="F5">
-        <v>79.27200000000001</v>
+        <v>105.696</v>
       </c>
       <c r="G5">
         <v>21.3</v>
@@ -1691,28 +1691,28 @@
         <v>225.6</v>
       </c>
       <c r="M5">
-        <v>3.9873816</v>
+        <v>5.3165088</v>
       </c>
       <c r="N5">
-        <v>221.6126184</v>
+        <v>220.2834912</v>
       </c>
       <c r="O5">
-        <v>55.90847278811727</v>
+        <v>55.57316032969479</v>
       </c>
       <c r="P5">
-        <v>165.7041456118827</v>
+        <v>164.7103308703052</v>
       </c>
       <c r="Q5">
-        <v>346.9041456118828</v>
+        <v>345.9103308703052</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1241507947468801</v>
+        <v>0.1247657032236938</v>
       </c>
       <c r="T5">
-        <v>0.6300601192798995</v>
+        <v>0.6350049230881963</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.57848248083404</v>
+        <v>42.43386186062553</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1212794873587145</v>
+        <v>0.1210043946149789</v>
       </c>
       <c r="C6">
-        <v>3278.430897611064</v>
+        <v>3264.307897874515</v>
       </c>
       <c r="D6">
-        <v>3362.826897611063</v>
+        <v>3375.127897874515</v>
       </c>
       <c r="E6">
-        <v>-2421.304</v>
+        <v>-2394.88</v>
       </c>
       <c r="F6">
-        <v>105.696</v>
+        <v>132.12</v>
       </c>
       <c r="G6">
         <v>21.3</v>
@@ -1773,28 +1773,28 @@
         <v>225.6</v>
       </c>
       <c r="M6">
-        <v>5.3165088</v>
+        <v>6.645636</v>
       </c>
       <c r="N6">
-        <v>220.2834912</v>
+        <v>218.954364</v>
       </c>
       <c r="O6">
-        <v>55.57316032969479</v>
+        <v>55.23784787127232</v>
       </c>
       <c r="P6">
-        <v>164.7103308703052</v>
+        <v>163.7165161287277</v>
       </c>
       <c r="Q6">
-        <v>345.9103308703052</v>
+        <v>344.9165161287277</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1247657032236938</v>
+        <v>0.1253935571421247</v>
       </c>
       <c r="T6">
-        <v>0.6350049230881963</v>
+        <v>0.6400538280292996</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.43386186062553</v>
+        <v>33.94708948850042</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1210043946149789</v>
+        <v>0.1207293018712434</v>
       </c>
       <c r="C7">
-        <v>3264.307897874515</v>
+        <v>3250.275221037783</v>
       </c>
       <c r="D7">
-        <v>3375.127897874515</v>
+        <v>3387.519221037783</v>
       </c>
       <c r="E7">
-        <v>-2394.88</v>
+        <v>-2368.456</v>
       </c>
       <c r="F7">
-        <v>132.12</v>
+        <v>158.544</v>
       </c>
       <c r="G7">
         <v>21.3</v>
@@ -1855,28 +1855,28 @@
         <v>225.6</v>
       </c>
       <c r="M7">
-        <v>6.645636</v>
+        <v>7.9747632</v>
       </c>
       <c r="N7">
-        <v>218.954364</v>
+        <v>217.6252368</v>
       </c>
       <c r="O7">
-        <v>55.23784787127232</v>
+        <v>54.90253541284984</v>
       </c>
       <c r="P7">
-        <v>163.7165161287277</v>
+        <v>162.7227013871502</v>
       </c>
       <c r="Q7">
-        <v>344.9165161287277</v>
+        <v>343.9227013871501</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1253935571421247</v>
+        <v>0.1260347696545647</v>
       </c>
       <c r="T7">
-        <v>0.6400538280292996</v>
+        <v>0.6452101564797879</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.94708948850042</v>
+        <v>28.28924124041702</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1207293018712434</v>
+        <v>0.1204542091275078</v>
       </c>
       <c r="C8">
-        <v>3250.275221037783</v>
+        <v>3236.333865591429</v>
       </c>
       <c r="D8">
-        <v>3387.519221037783</v>
+        <v>3400.001865591428</v>
       </c>
       <c r="E8">
-        <v>-2368.456</v>
+        <v>-2342.032</v>
       </c>
       <c r="F8">
-        <v>158.544</v>
+        <v>184.968</v>
       </c>
       <c r="G8">
         <v>21.3</v>
@@ -1937,28 +1937,28 @@
         <v>225.6</v>
       </c>
       <c r="M8">
-        <v>7.9747632</v>
+        <v>9.303890399999998</v>
       </c>
       <c r="N8">
-        <v>217.6252368</v>
+        <v>216.2961096</v>
       </c>
       <c r="O8">
-        <v>54.90253541284984</v>
+        <v>54.56722295442736</v>
       </c>
       <c r="P8">
-        <v>162.7227013871502</v>
+        <v>161.7288866455726</v>
       </c>
       <c r="Q8">
-        <v>343.9227013871501</v>
+        <v>342.9288866455727</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1260347696545647</v>
+        <v>0.1266897716834012</v>
       </c>
       <c r="T8">
-        <v>0.6452101564797879</v>
+        <v>0.6504773737141577</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.28924124041702</v>
+        <v>24.24792106321459</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1204542091275078</v>
+        <v>0.1201791163837723</v>
       </c>
       <c r="C9">
-        <v>3236.333865591429</v>
+        <v>3222.484844797763</v>
       </c>
       <c r="D9">
-        <v>3400.001865591428</v>
+        <v>3412.576844797763</v>
       </c>
       <c r="E9">
-        <v>-2342.032</v>
+        <v>-2315.608</v>
       </c>
       <c r="F9">
-        <v>184.968</v>
+        <v>211.392</v>
       </c>
       <c r="G9">
         <v>21.3</v>
@@ -2019,28 +2019,28 @@
         <v>225.6</v>
       </c>
       <c r="M9">
-        <v>9.3038904</v>
+        <v>10.6330176</v>
       </c>
       <c r="N9">
-        <v>216.2961096</v>
+        <v>214.9669824</v>
       </c>
       <c r="O9">
-        <v>54.56722295442736</v>
+        <v>54.23191049600489</v>
       </c>
       <c r="P9">
-        <v>161.7288866455726</v>
+        <v>160.7350719039951</v>
       </c>
       <c r="Q9">
-        <v>342.9288866455727</v>
+        <v>341.9350719039951</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1266897716834012</v>
+        <v>0.1273590128867777</v>
       </c>
       <c r="T9">
-        <v>0.6504773737141577</v>
+        <v>0.6558590956710139</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.24792106321459</v>
+        <v>21.21693093031276</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1201791163837723</v>
+        <v>0.1199040236400368</v>
       </c>
       <c r="C10">
-        <v>3222.484844797763</v>
+        <v>3208.729186965038</v>
       </c>
       <c r="D10">
-        <v>3412.576844797763</v>
+        <v>3425.245186965037</v>
       </c>
       <c r="E10">
-        <v>-2315.608</v>
+        <v>-2289.184</v>
       </c>
       <c r="F10">
-        <v>211.392</v>
+        <v>237.816</v>
       </c>
       <c r="G10">
         <v>21.3</v>
@@ -2101,28 +2101,28 @@
         <v>225.6</v>
       </c>
       <c r="M10">
-        <v>10.6330176</v>
+        <v>11.9621448</v>
       </c>
       <c r="N10">
-        <v>214.9669824</v>
+        <v>213.6378552</v>
       </c>
       <c r="O10">
-        <v>54.23191049600489</v>
+        <v>53.8965980375824</v>
       </c>
       <c r="P10">
-        <v>160.7350719039951</v>
+        <v>159.7412571624176</v>
       </c>
       <c r="Q10">
-        <v>341.9350719039951</v>
+        <v>340.9412571624176</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1273590128867777</v>
+        <v>0.1280429626880306</v>
       </c>
       <c r="T10">
-        <v>0.6558590956710139</v>
+        <v>0.6613590972313174</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.21693093031276</v>
+        <v>18.85949416027801</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1199040236400368</v>
+        <v>0.1196289308963012</v>
       </c>
       <c r="C11">
-        <v>3208.729186965038</v>
+        <v>3195.06793572775</v>
       </c>
       <c r="D11">
-        <v>3425.245186965037</v>
+        <v>3438.00793572775</v>
       </c>
       <c r="E11">
-        <v>-2289.184</v>
+        <v>-2262.76</v>
       </c>
       <c r="F11">
-        <v>237.816</v>
+        <v>264.24</v>
       </c>
       <c r="G11">
         <v>21.3</v>
@@ -2183,28 +2183,28 @@
         <v>225.6</v>
       </c>
       <c r="M11">
-        <v>11.9621448</v>
+        <v>13.291272</v>
       </c>
       <c r="N11">
-        <v>213.6378552</v>
+        <v>212.308728</v>
       </c>
       <c r="O11">
-        <v>53.8965980375824</v>
+        <v>53.56128557915993</v>
       </c>
       <c r="P11">
-        <v>159.7412571624176</v>
+        <v>158.7474424208401</v>
       </c>
       <c r="Q11">
-        <v>340.9412571624176</v>
+        <v>339.94744242084</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1280429626880306</v>
+        <v>0.1287421113737558</v>
       </c>
       <c r="T11">
-        <v>0.6613590972313174</v>
+        <v>0.6669813210485166</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.85949416027801</v>
+        <v>16.97354474425021</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1196289308963012</v>
+        <v>0.1193538381525657</v>
       </c>
       <c r="C12">
-        <v>3195.06793572775</v>
+        <v>3181.502150333251</v>
       </c>
       <c r="D12">
-        <v>3438.00793572775</v>
+        <v>3450.866150333251</v>
       </c>
       <c r="E12">
-        <v>-2262.76</v>
+        <v>-2236.336</v>
       </c>
       <c r="F12">
-        <v>264.24</v>
+        <v>290.664</v>
       </c>
       <c r="G12">
         <v>21.3</v>
@@ -2265,28 +2265,28 @@
         <v>225.6</v>
       </c>
       <c r="M12">
-        <v>13.291272</v>
+        <v>14.6203992</v>
       </c>
       <c r="N12">
-        <v>212.308728</v>
+        <v>210.9796008</v>
       </c>
       <c r="O12">
-        <v>53.56128557915993</v>
+        <v>53.22597312073744</v>
       </c>
       <c r="P12">
-        <v>158.7474424208401</v>
+        <v>157.7536276792625</v>
       </c>
       <c r="Q12">
-        <v>339.94744242084</v>
+        <v>338.9536276792626</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1287421113737558</v>
+        <v>0.1294569712659018</v>
       </c>
       <c r="T12">
-        <v>0.6669813210485166</v>
+        <v>0.6727298869739674</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.97354474425021</v>
+        <v>15.43049522204565</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1193538381525657</v>
+        <v>0.1190787454088301</v>
       </c>
       <c r="C13">
-        <v>3181.502150333251</v>
+        <v>3168.032905934797</v>
       </c>
       <c r="D13">
-        <v>3450.866150333251</v>
+        <v>3463.820905934797</v>
       </c>
       <c r="E13">
-        <v>-2236.336</v>
+        <v>-2209.912</v>
       </c>
       <c r="F13">
-        <v>290.664</v>
+        <v>317.088</v>
       </c>
       <c r="G13">
         <v>21.3</v>
@@ -2347,28 +2347,28 @@
         <v>225.6</v>
       </c>
       <c r="M13">
-        <v>14.6203992</v>
+        <v>15.9495264</v>
       </c>
       <c r="N13">
-        <v>210.9796008</v>
+        <v>209.6504736</v>
       </c>
       <c r="O13">
-        <v>53.22597312073744</v>
+        <v>52.89066066231497</v>
       </c>
       <c r="P13">
-        <v>157.7536276792625</v>
+        <v>156.759812937685</v>
       </c>
       <c r="Q13">
-        <v>338.9536276792626</v>
+        <v>337.959812937685</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1294569712659018</v>
+        <v>0.1301880779737783</v>
       </c>
       <c r="T13">
-        <v>0.6727298869739674</v>
+        <v>0.6786091021249966</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.43049522204565</v>
+        <v>14.14462062020851</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1190787454088301</v>
+        <v>0.1188036526650946</v>
       </c>
       <c r="C14">
-        <v>3168.032905934797</v>
+        <v>3154.661293891239</v>
       </c>
       <c r="D14">
-        <v>3463.820905934797</v>
+        <v>3476.873293891239</v>
       </c>
       <c r="E14">
-        <v>-2209.912</v>
+        <v>-2183.488</v>
       </c>
       <c r="F14">
-        <v>317.088</v>
+        <v>343.512</v>
       </c>
       <c r="G14">
         <v>21.3</v>
@@ -2429,28 +2429,28 @@
         <v>225.6</v>
       </c>
       <c r="M14">
-        <v>15.9495264</v>
+        <v>17.2786536</v>
       </c>
       <c r="N14">
-        <v>209.6504736</v>
+        <v>208.3213464</v>
       </c>
       <c r="O14">
-        <v>52.89066066231497</v>
+        <v>52.55534820389249</v>
       </c>
       <c r="P14">
-        <v>156.759812937685</v>
+        <v>155.7659981961075</v>
       </c>
       <c r="Q14">
-        <v>337.959812937685</v>
+        <v>336.9659981961075</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1301880779737783</v>
+        <v>0.1309359917324107</v>
       </c>
       <c r="T14">
-        <v>0.6786091021249966</v>
+        <v>0.6846234716473139</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.14462062020851</v>
+        <v>13.05657288019247</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1188036526650946</v>
+        <v>0.1186855810821112</v>
       </c>
       <c r="C15">
-        <v>3154.661293891239</v>
+        <v>3133.869682733414</v>
       </c>
       <c r="D15">
-        <v>3476.873293891239</v>
+        <v>3482.505682733414</v>
       </c>
       <c r="E15">
-        <v>-2183.488</v>
+        <v>-2157.064</v>
       </c>
       <c r="F15">
-        <v>343.512</v>
+        <v>369.936</v>
       </c>
       <c r="G15">
         <v>21.3</v>
@@ -2511,45 +2511,45 @@
         <v>225.6</v>
       </c>
       <c r="M15">
-        <v>17.2786536</v>
+        <v>19.1626848</v>
       </c>
       <c r="N15">
-        <v>208.3213464</v>
+        <v>206.4373152</v>
       </c>
       <c r="O15">
-        <v>52.55534820389249</v>
+        <v>52.08004446064155</v>
       </c>
       <c r="P15">
-        <v>155.7659981961075</v>
+        <v>154.3572707393585</v>
       </c>
       <c r="Q15">
-        <v>336.9659981961075</v>
+        <v>335.5572707393585</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1309359917324107</v>
+        <v>0.131701298834267</v>
       </c>
       <c r="T15">
-        <v>0.6846234716473139</v>
+        <v>0.6907777102282898</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.2522801868944358</v>
       </c>
       <c r="W15">
-        <v>0.03761030659920988</v>
+        <v>0.03873188631886822</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.05657288019247</v>
+        <v>11.77288059343334</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1186855810821112</v>
+        <v>0.1184217041355722</v>
       </c>
       <c r="C16">
-        <v>3133.869682733414</v>
+        <v>3120.099654115699</v>
       </c>
       <c r="D16">
-        <v>3482.505682733414</v>
+        <v>3495.159654115699</v>
       </c>
       <c r="E16">
-        <v>-2157.064</v>
+        <v>-2130.64</v>
       </c>
       <c r="F16">
-        <v>369.936</v>
+        <v>396.3600000000001</v>
       </c>
       <c r="G16">
         <v>21.3</v>
@@ -2593,28 +2593,28 @@
         <v>225.6</v>
       </c>
       <c r="M16">
-        <v>19.1626848</v>
+        <v>20.531448</v>
       </c>
       <c r="N16">
-        <v>206.4373152</v>
+        <v>205.068552</v>
       </c>
       <c r="O16">
-        <v>52.08004446064155</v>
+        <v>51.73473262473131</v>
       </c>
       <c r="P16">
-        <v>154.3572707393585</v>
+        <v>153.3338193752687</v>
       </c>
       <c r="Q16">
-        <v>335.5572707393585</v>
+        <v>334.5338193752686</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.131701298834267</v>
+        <v>0.1324846131620494</v>
       </c>
       <c r="T16">
-        <v>0.6907777102282898</v>
+        <v>0.6970767544229356</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.77288059343334</v>
+        <v>10.98802188720444</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1184217041355722</v>
+        <v>0.1181578271890333</v>
       </c>
       <c r="C17">
-        <v>3120.099654115699</v>
+        <v>3106.421919350901</v>
       </c>
       <c r="D17">
-        <v>3495.159654115699</v>
+        <v>3507.905919350901</v>
       </c>
       <c r="E17">
-        <v>-2130.64</v>
+        <v>-2104.216</v>
       </c>
       <c r="F17">
-        <v>396.36</v>
+        <v>422.784</v>
       </c>
       <c r="G17">
         <v>21.3</v>
@@ -2675,28 +2675,28 @@
         <v>225.6</v>
       </c>
       <c r="M17">
-        <v>20.531448</v>
+        <v>21.9002112</v>
       </c>
       <c r="N17">
-        <v>205.068552</v>
+        <v>203.6997888</v>
       </c>
       <c r="O17">
-        <v>51.73473262473131</v>
+        <v>51.38942078882109</v>
       </c>
       <c r="P17">
-        <v>153.3338193752687</v>
+        <v>152.3103680111789</v>
       </c>
       <c r="Q17">
-        <v>334.5338193752686</v>
+        <v>333.5103680111789</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1324846131620494</v>
+        <v>0.1332865778309694</v>
       </c>
       <c r="T17">
-        <v>0.6970767544229356</v>
+        <v>0.7035257758603111</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.98802188720445</v>
+        <v>10.30127051925417</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1181578271890333</v>
+        <v>0.1181100412684818</v>
       </c>
       <c r="C18">
-        <v>3106.421919350901</v>
+        <v>3082.316110719948</v>
       </c>
       <c r="D18">
-        <v>3507.905919350901</v>
+        <v>3510.224110719947</v>
       </c>
       <c r="E18">
-        <v>-2104.216</v>
+        <v>-2077.792</v>
       </c>
       <c r="F18">
-        <v>422.784</v>
+        <v>449.208</v>
       </c>
       <c r="G18">
         <v>21.3</v>
@@ -2757,45 +2757,45 @@
         <v>225.6</v>
       </c>
       <c r="M18">
-        <v>21.9002112</v>
+        <v>24.032628</v>
       </c>
       <c r="N18">
-        <v>203.6997888</v>
+        <v>201.567372</v>
       </c>
       <c r="O18">
-        <v>51.38942078882109</v>
+        <v>50.85145427998025</v>
       </c>
       <c r="P18">
-        <v>152.3103680111789</v>
+        <v>150.7159177200197</v>
       </c>
       <c r="Q18">
-        <v>333.5103680111789</v>
+        <v>331.9159177200197</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1332865778309694</v>
+        <v>0.134107866949743</v>
       </c>
       <c r="T18">
-        <v>0.7035257758603111</v>
+        <v>0.7101301954046113</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.2522801868944358</v>
       </c>
       <c r="W18">
-        <v>0.03873188631886822</v>
+        <v>0.04000301000114768</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.30127051925417</v>
+        <v>9.387238049871199</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1181100412684818</v>
+        <v>0.1178588755587656</v>
       </c>
       <c r="C19">
-        <v>3082.316110719948</v>
+        <v>3068.127216016765</v>
       </c>
       <c r="D19">
-        <v>3510.224110719947</v>
+        <v>3522.459216016764</v>
       </c>
       <c r="E19">
-        <v>-2077.792</v>
+        <v>-2051.368</v>
       </c>
       <c r="F19">
-        <v>449.208</v>
+        <v>475.6320000000001</v>
       </c>
       <c r="G19">
         <v>21.3</v>
@@ -2839,28 +2839,28 @@
         <v>225.6</v>
       </c>
       <c r="M19">
-        <v>24.032628</v>
+        <v>25.446312</v>
       </c>
       <c r="N19">
-        <v>201.567372</v>
+        <v>200.153688</v>
       </c>
       <c r="O19">
-        <v>50.85145427998025</v>
+        <v>50.49480981625058</v>
       </c>
       <c r="P19">
-        <v>150.7159177200197</v>
+        <v>149.6588781837494</v>
       </c>
       <c r="Q19">
-        <v>331.9159177200197</v>
+        <v>330.8588781837494</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.134107866949743</v>
+        <v>0.1349491875104379</v>
       </c>
       <c r="T19">
-        <v>0.7101301954046113</v>
+        <v>0.7168956983524311</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.387238049871199</v>
+        <v>8.865724824878354</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1178588755587657</v>
+        <v>0.1176077098490495</v>
       </c>
       <c r="C20">
-        <v>3068.127216016764</v>
+        <v>3054.023912092394</v>
       </c>
       <c r="D20">
-        <v>3522.459216016764</v>
+        <v>3534.779912092394</v>
       </c>
       <c r="E20">
-        <v>-2051.368</v>
+        <v>-2024.944</v>
       </c>
       <c r="F20">
-        <v>475.632</v>
+        <v>502.056</v>
       </c>
       <c r="G20">
         <v>21.3</v>
@@ -2921,28 +2921,28 @@
         <v>225.6</v>
       </c>
       <c r="M20">
-        <v>25.446312</v>
+        <v>26.859996</v>
       </c>
       <c r="N20">
-        <v>200.153688</v>
+        <v>198.740004</v>
       </c>
       <c r="O20">
-        <v>50.49480981625058</v>
+        <v>50.13816535252091</v>
       </c>
       <c r="P20">
-        <v>149.6588781837494</v>
+        <v>148.6018386474791</v>
       </c>
       <c r="Q20">
-        <v>330.8588781837494</v>
+        <v>329.8018386474791</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1349491875104379</v>
+        <v>0.1358112814183104</v>
       </c>
       <c r="T20">
-        <v>0.7168956983524311</v>
+        <v>0.7238282507557525</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.865724824878356</v>
+        <v>8.399107728832126</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1176077098490495</v>
+        <v>0.1173565441393333</v>
       </c>
       <c r="C21">
-        <v>3054.023912092394</v>
+        <v>3040.007100225773</v>
       </c>
       <c r="D21">
-        <v>3534.779912092394</v>
+        <v>3547.187100225773</v>
       </c>
       <c r="E21">
-        <v>-2024.944</v>
+        <v>-1998.52</v>
       </c>
       <c r="F21">
-        <v>502.056</v>
+        <v>528.48</v>
       </c>
       <c r="G21">
         <v>21.3</v>
@@ -3003,28 +3003,28 @@
         <v>225.6</v>
       </c>
       <c r="M21">
-        <v>26.859996</v>
+        <v>28.27368</v>
       </c>
       <c r="N21">
-        <v>198.740004</v>
+        <v>197.32632</v>
       </c>
       <c r="O21">
-        <v>50.13816535252091</v>
+        <v>49.78152088879124</v>
       </c>
       <c r="P21">
-        <v>148.6018386474791</v>
+        <v>147.5447991112088</v>
       </c>
       <c r="Q21">
-        <v>329.8018386474791</v>
+        <v>328.7447991112087</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1358112814183104</v>
+        <v>0.1366949276738797</v>
       </c>
       <c r="T21">
-        <v>0.7238282507557525</v>
+        <v>0.730934116969157</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.399107728832126</v>
+        <v>7.97915234239052</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1173565441393333</v>
+        <v>0.1172309953582189</v>
       </c>
       <c r="C22">
-        <v>3040.007100225773</v>
+        <v>3019.817718889349</v>
       </c>
       <c r="D22">
-        <v>3547.187100225773</v>
+        <v>3553.421718889349</v>
       </c>
       <c r="E22">
-        <v>-1998.52</v>
+        <v>-1972.096</v>
       </c>
       <c r="F22">
-        <v>528.48</v>
+        <v>554.9040000000001</v>
       </c>
       <c r="G22">
         <v>21.3</v>
@@ -3085,45 +3085,45 @@
         <v>225.6</v>
       </c>
       <c r="M22">
-        <v>28.27368</v>
+        <v>30.13128720000001</v>
       </c>
       <c r="N22">
-        <v>197.32632</v>
+        <v>195.4687128</v>
       </c>
       <c r="O22">
-        <v>49.78152088879124</v>
+        <v>49.31288339719879</v>
       </c>
       <c r="P22">
-        <v>147.5447991112088</v>
+        <v>146.1558294028012</v>
       </c>
       <c r="Q22">
-        <v>328.7447991112087</v>
+        <v>327.3558294028012</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1366949276738797</v>
+        <v>0.1376009447207293</v>
       </c>
       <c r="T22">
-        <v>0.730934116969157</v>
+        <v>0.7382198785297364</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.2522801868944358</v>
       </c>
       <c r="W22">
-        <v>0.04000301000114768</v>
+        <v>0.04060118585163214</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.97915234239052</v>
+        <v>7.48723406678756</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1172309953582189</v>
+        <v>0.1169858114070076</v>
       </c>
       <c r="C23">
-        <v>3019.817718889349</v>
+        <v>3005.632702475221</v>
       </c>
       <c r="D23">
-        <v>3553.421718889349</v>
+        <v>3565.660702475221</v>
       </c>
       <c r="E23">
-        <v>-1972.096</v>
+        <v>-1945.672</v>
       </c>
       <c r="F23">
-        <v>554.904</v>
+        <v>581.328</v>
       </c>
       <c r="G23">
         <v>21.3</v>
@@ -3167,28 +3167,28 @@
         <v>225.6</v>
       </c>
       <c r="M23">
-        <v>30.1312872</v>
+        <v>31.5661104</v>
       </c>
       <c r="N23">
-        <v>195.4687128</v>
+        <v>194.0338896</v>
       </c>
       <c r="O23">
-        <v>49.31288339719879</v>
+        <v>48.95090593214232</v>
       </c>
       <c r="P23">
-        <v>146.1558294028012</v>
+        <v>145.0829836678577</v>
       </c>
       <c r="Q23">
-        <v>327.3558294028012</v>
+        <v>326.2829836678577</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1376009447207293</v>
+        <v>0.1385301929739083</v>
       </c>
       <c r="T23">
-        <v>0.7382198785297364</v>
+        <v>0.7456924544893049</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.487234066787561</v>
+        <v>7.146905245569946</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1169858114070076</v>
+        <v>0.1167406274557963</v>
       </c>
       <c r="C24">
-        <v>3005.632702475221</v>
+        <v>2991.532286450519</v>
       </c>
       <c r="D24">
-        <v>3565.660702475221</v>
+        <v>3577.984286450519</v>
       </c>
       <c r="E24">
-        <v>-1945.672</v>
+        <v>-1919.248</v>
       </c>
       <c r="F24">
-        <v>581.328</v>
+        <v>607.7520000000001</v>
       </c>
       <c r="G24">
         <v>21.3</v>
@@ -3249,28 +3249,28 @@
         <v>225.6</v>
       </c>
       <c r="M24">
-        <v>31.5661104</v>
+        <v>33.0009336</v>
       </c>
       <c r="N24">
-        <v>194.0338896</v>
+        <v>192.5990664</v>
       </c>
       <c r="O24">
-        <v>48.95090593214232</v>
+        <v>48.58892846708584</v>
       </c>
       <c r="P24">
-        <v>145.0829836678577</v>
+        <v>144.0101379329141</v>
       </c>
       <c r="Q24">
-        <v>326.2829836678577</v>
+        <v>325.2101379329142</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1385301929739083</v>
+        <v>0.1394835775453518</v>
       </c>
       <c r="T24">
-        <v>0.7456924544893049</v>
+        <v>0.7533591233309401</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.146905245569946</v>
+        <v>6.83617023489299</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1167406274557963</v>
+        <v>0.1164954435045849</v>
       </c>
       <c r="C25">
-        <v>2991.532286450519</v>
+        <v>2977.517351041324</v>
       </c>
       <c r="D25">
-        <v>3577.984286450519</v>
+        <v>3590.393351041324</v>
       </c>
       <c r="E25">
-        <v>-1919.248</v>
+        <v>-1892.824</v>
       </c>
       <c r="F25">
-        <v>607.7520000000001</v>
+        <v>634.176</v>
       </c>
       <c r="G25">
         <v>21.3</v>
@@ -3331,28 +3331,28 @@
         <v>225.6</v>
       </c>
       <c r="M25">
-        <v>33.0009336</v>
+        <v>34.4357568</v>
       </c>
       <c r="N25">
-        <v>192.5990664</v>
+        <v>191.1642432</v>
       </c>
       <c r="O25">
-        <v>48.58892846708584</v>
+        <v>48.22695100202937</v>
       </c>
       <c r="P25">
-        <v>144.0101379329141</v>
+        <v>142.9372921979706</v>
       </c>
       <c r="Q25">
-        <v>325.2101379329142</v>
+        <v>324.1372921979706</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1394835775453518</v>
+        <v>0.1404620511844648</v>
       </c>
       <c r="T25">
-        <v>0.7533591233309401</v>
+        <v>0.7612275466157763</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.83617023489299</v>
+        <v>6.551329808439116</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1164954435045849</v>
+        <v>0.1162502595533736</v>
       </c>
       <c r="C26">
-        <v>2977.517351041324</v>
+        <v>2963.588788727316</v>
       </c>
       <c r="D26">
-        <v>3590.393351041324</v>
+        <v>3602.888788727316</v>
       </c>
       <c r="E26">
-        <v>-1892.824</v>
+        <v>-1866.4</v>
       </c>
       <c r="F26">
-        <v>634.176</v>
+        <v>660.6</v>
       </c>
       <c r="G26">
         <v>21.3</v>
@@ -3413,28 +3413,28 @@
         <v>225.6</v>
       </c>
       <c r="M26">
-        <v>34.4357568</v>
+        <v>35.87058</v>
       </c>
       <c r="N26">
-        <v>191.1642432</v>
+        <v>189.72942</v>
       </c>
       <c r="O26">
-        <v>48.22695100202937</v>
+        <v>47.8649735369729</v>
       </c>
       <c r="P26">
-        <v>142.9372921979706</v>
+        <v>141.8644464630271</v>
       </c>
       <c r="Q26">
-        <v>324.1372921979706</v>
+        <v>323.0644464630271</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1404620511844648</v>
+        <v>0.1414666174539541</v>
       </c>
       <c r="T26">
-        <v>0.7612275466157763</v>
+        <v>0.7693057945215414</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.551329808439116</v>
+        <v>6.289276616101551</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1162502595533736</v>
+        <v>0.1161994827535697</v>
       </c>
       <c r="C27">
-        <v>2963.588788727316</v>
+        <v>2939.763432290952</v>
       </c>
       <c r="D27">
-        <v>3602.888788727316</v>
+        <v>3605.487432290952</v>
       </c>
       <c r="E27">
-        <v>-1866.4</v>
+        <v>-1839.976</v>
       </c>
       <c r="F27">
-        <v>660.6</v>
+        <v>687.024</v>
       </c>
       <c r="G27">
         <v>21.3</v>
@@ -3495,45 +3495,45 @@
         <v>225.6</v>
       </c>
       <c r="M27">
-        <v>35.87058</v>
+        <v>37.9924272</v>
       </c>
       <c r="N27">
-        <v>189.72942</v>
+        <v>187.6075728</v>
       </c>
       <c r="O27">
-        <v>47.8649735369729</v>
+        <v>47.32967352879546</v>
       </c>
       <c r="P27">
-        <v>141.8644464630271</v>
+        <v>140.2778992712045</v>
       </c>
       <c r="Q27">
-        <v>323.0644464630271</v>
+        <v>321.4778992712045</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1414666174539541</v>
+        <v>0.1424983341631594</v>
       </c>
       <c r="T27">
-        <v>0.7693057945215414</v>
+        <v>0.7776023734517865</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.2522801868944358</v>
       </c>
       <c r="W27">
-        <v>0.04060118585163214</v>
+        <v>0.0413489056647377</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.289276616101551</v>
+        <v>5.938025459979034</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1161994827535697</v>
+        <v>0.1159617760004895</v>
       </c>
       <c r="C28">
-        <v>2939.763432290952</v>
+        <v>2925.554754645329</v>
       </c>
       <c r="D28">
-        <v>3605.487432290952</v>
+        <v>3617.702754645329</v>
       </c>
       <c r="E28">
-        <v>-1839.976</v>
+        <v>-1813.552</v>
       </c>
       <c r="F28">
-        <v>687.024</v>
+        <v>713.4480000000001</v>
       </c>
       <c r="G28">
         <v>21.3</v>
@@ -3577,28 +3577,28 @@
         <v>225.6</v>
       </c>
       <c r="M28">
-        <v>37.9924272</v>
+        <v>39.4536744</v>
       </c>
       <c r="N28">
-        <v>187.6075728</v>
+        <v>186.1463256</v>
       </c>
       <c r="O28">
-        <v>47.32967352879546</v>
+        <v>46.96102981208049</v>
       </c>
       <c r="P28">
-        <v>140.2778992712045</v>
+        <v>139.1852957879195</v>
       </c>
       <c r="Q28">
-        <v>321.4778992712045</v>
+        <v>320.3852957879195</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1424983341631594</v>
+        <v>0.1435583170835757</v>
       </c>
       <c r="T28">
-        <v>0.7776023734517865</v>
+        <v>0.7861262559143674</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.938025459979034</v>
+        <v>5.718098591090921</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1159617760004895</v>
+        <v>0.1157240692474092</v>
       </c>
       <c r="C29">
-        <v>2925.554754645329</v>
+        <v>2911.429128934354</v>
       </c>
       <c r="D29">
-        <v>3617.702754645329</v>
+        <v>3630.001128934353</v>
       </c>
       <c r="E29">
-        <v>-1813.552</v>
+        <v>-1787.128</v>
       </c>
       <c r="F29">
-        <v>713.4480000000001</v>
+        <v>739.8720000000001</v>
       </c>
       <c r="G29">
         <v>21.3</v>
@@ -3659,28 +3659,28 @@
         <v>225.6</v>
       </c>
       <c r="M29">
-        <v>39.4536744</v>
+        <v>40.91492160000001</v>
       </c>
       <c r="N29">
-        <v>186.1463256</v>
+        <v>184.6850784</v>
       </c>
       <c r="O29">
-        <v>46.96102981208049</v>
+        <v>46.59238609536552</v>
       </c>
       <c r="P29">
-        <v>139.1852957879195</v>
+        <v>138.0926923046345</v>
       </c>
       <c r="Q29">
-        <v>320.3852957879195</v>
+        <v>319.2926923046344</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1435583170835757</v>
+        <v>0.1446477439740037</v>
       </c>
       <c r="T29">
-        <v>0.7861262559143674</v>
+        <v>0.7948869128897975</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.718098591090921</v>
+        <v>5.513880784266245</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1157240692474092</v>
+        <v>0.1154863624943289</v>
       </c>
       <c r="C30">
-        <v>2911.429128934354</v>
+        <v>2897.387405051964</v>
       </c>
       <c r="D30">
-        <v>3630.001128934353</v>
+        <v>3642.383405051964</v>
       </c>
       <c r="E30">
-        <v>-1787.128</v>
+        <v>-1760.704</v>
       </c>
       <c r="F30">
-        <v>739.8720000000001</v>
+        <v>766.2960000000002</v>
       </c>
       <c r="G30">
         <v>21.3</v>
@@ -3741,28 +3741,28 @@
         <v>225.6</v>
       </c>
       <c r="M30">
-        <v>40.91492160000001</v>
+        <v>42.37616880000001</v>
       </c>
       <c r="N30">
-        <v>184.6850784</v>
+        <v>183.2238312</v>
       </c>
       <c r="O30">
-        <v>46.59238609536552</v>
+        <v>46.22374237865055</v>
       </c>
       <c r="P30">
-        <v>138.0926923046345</v>
+        <v>137.0000888213494</v>
       </c>
       <c r="Q30">
-        <v>319.2926923046344</v>
+        <v>318.2000888213495</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1446477439740037</v>
+        <v>0.1457678589458521</v>
       </c>
       <c r="T30">
-        <v>0.7948869128897975</v>
+        <v>0.8038943489349581</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.513880784266245</v>
+        <v>5.323746964119134</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1154863624943289</v>
+        <v>0.1152486557412486</v>
       </c>
       <c r="C31">
-        <v>2897.387405051964</v>
+        <v>2883.430444528067</v>
       </c>
       <c r="D31">
-        <v>3642.383405051964</v>
+        <v>3654.850444528067</v>
       </c>
       <c r="E31">
-        <v>-1760.704</v>
+        <v>-1734.28</v>
       </c>
       <c r="F31">
-        <v>766.2959999999999</v>
+        <v>792.72</v>
       </c>
       <c r="G31">
         <v>21.3</v>
@@ -3823,28 +3823,28 @@
         <v>225.6</v>
       </c>
       <c r="M31">
-        <v>42.37616879999999</v>
+        <v>43.837416</v>
       </c>
       <c r="N31">
-        <v>183.2238312</v>
+        <v>181.762584</v>
       </c>
       <c r="O31">
-        <v>46.22374237865056</v>
+        <v>45.85509866193558</v>
       </c>
       <c r="P31">
-        <v>137.0000888213494</v>
+        <v>135.9074853380644</v>
       </c>
       <c r="Q31">
-        <v>318.2000888213495</v>
+        <v>317.1074853380644</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1457678589458521</v>
+        <v>0.1469199772026105</v>
       </c>
       <c r="T31">
-        <v>0.8038943489349581</v>
+        <v>0.8131591402956947</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.323746964119136</v>
+        <v>5.14628873198183</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1152486557412486</v>
+        <v>0.1150109489881684</v>
       </c>
       <c r="C32">
-        <v>2883.430444528067</v>
+        <v>2869.559120728348</v>
       </c>
       <c r="D32">
-        <v>3654.850444528067</v>
+        <v>3667.403120728347</v>
       </c>
       <c r="E32">
-        <v>-1734.28</v>
+        <v>-1707.856</v>
       </c>
       <c r="F32">
-        <v>792.72</v>
+        <v>819.144</v>
       </c>
       <c r="G32">
         <v>21.3</v>
@@ -3905,28 +3905,28 @@
         <v>225.6</v>
       </c>
       <c r="M32">
-        <v>43.837416</v>
+        <v>45.2986632</v>
       </c>
       <c r="N32">
-        <v>181.762584</v>
+        <v>180.3013368</v>
       </c>
       <c r="O32">
-        <v>45.85509866193558</v>
+        <v>45.48645494522061</v>
       </c>
       <c r="P32">
-        <v>135.9074853380644</v>
+        <v>134.8148818547794</v>
       </c>
       <c r="Q32">
-        <v>317.1074853380644</v>
+        <v>316.0148818547794</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1469199772026105</v>
+        <v>0.1481054901914489</v>
       </c>
       <c r="T32">
-        <v>0.8131591402956947</v>
+        <v>0.8226924763335542</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.14628873198183</v>
+        <v>4.980279418046933</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1150109489881684</v>
+        <v>0.1147732422350881</v>
       </c>
       <c r="C33">
-        <v>2869.559120728348</v>
+        <v>2855.774319058238</v>
       </c>
       <c r="D33">
-        <v>3667.403120728347</v>
+        <v>3680.042319058238</v>
       </c>
       <c r="E33">
-        <v>-1707.856</v>
+        <v>-1681.432</v>
       </c>
       <c r="F33">
-        <v>819.144</v>
+        <v>845.5680000000001</v>
       </c>
       <c r="G33">
         <v>21.3</v>
@@ -3987,28 +3987,28 @@
         <v>225.6</v>
       </c>
       <c r="M33">
-        <v>45.2986632</v>
+        <v>46.75991040000001</v>
       </c>
       <c r="N33">
-        <v>180.3013368</v>
+        <v>178.8400896</v>
       </c>
       <c r="O33">
-        <v>45.48645494522061</v>
+        <v>45.11781122850564</v>
       </c>
       <c r="P33">
-        <v>134.8148818547794</v>
+        <v>133.7222783714944</v>
       </c>
       <c r="Q33">
-        <v>316.0148818547794</v>
+        <v>314.9222783714944</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1481054901914489</v>
+        <v>0.1493258712093707</v>
       </c>
       <c r="T33">
-        <v>0.8226924763335542</v>
+        <v>0.8325062046078213</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.980279418046933</v>
+        <v>4.824645686232965</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1147732422350881</v>
+        <v>0.1145355354820078</v>
       </c>
       <c r="C34">
-        <v>2855.774319058238</v>
+        <v>2842.076937171081</v>
       </c>
       <c r="D34">
-        <v>3680.042319058238</v>
+        <v>3692.768937171081</v>
       </c>
       <c r="E34">
-        <v>-1681.432</v>
+        <v>-1655.008</v>
       </c>
       <c r="F34">
-        <v>845.5680000000001</v>
+        <v>871.9920000000001</v>
       </c>
       <c r="G34">
         <v>21.3</v>
@@ -4069,28 +4069,28 @@
         <v>225.6</v>
       </c>
       <c r="M34">
-        <v>46.75991040000001</v>
+        <v>48.22115760000001</v>
       </c>
       <c r="N34">
-        <v>178.8400896</v>
+        <v>177.3788424</v>
       </c>
       <c r="O34">
-        <v>45.11781122850564</v>
+        <v>44.74916751179067</v>
       </c>
       <c r="P34">
-        <v>133.7222783714944</v>
+        <v>132.6296748882093</v>
       </c>
       <c r="Q34">
-        <v>314.9222783714944</v>
+        <v>313.8296748882094</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1493258712093707</v>
+        <v>0.1505826815114096</v>
       </c>
       <c r="T34">
-        <v>0.8325062046078213</v>
+        <v>0.8426128799947531</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.824645686232965</v>
+        <v>4.678444301801663</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1145355354820078</v>
+        <v>0.1142978287289276</v>
       </c>
       <c r="C35">
-        <v>2842.076937171081</v>
+        <v>2828.467885180665</v>
       </c>
       <c r="D35">
-        <v>3692.768937171081</v>
+        <v>3705.583885180665</v>
       </c>
       <c r="E35">
-        <v>-1655.008</v>
+        <v>-1628.584</v>
       </c>
       <c r="F35">
-        <v>871.9920000000001</v>
+        <v>898.4160000000001</v>
       </c>
       <c r="G35">
         <v>21.3</v>
@@ -4151,28 +4151,28 @@
         <v>225.6</v>
       </c>
       <c r="M35">
-        <v>48.22115760000001</v>
+        <v>49.68240480000001</v>
       </c>
       <c r="N35">
-        <v>177.3788424</v>
+        <v>175.9175952</v>
       </c>
       <c r="O35">
-        <v>44.74916751179067</v>
+        <v>44.3805237950757</v>
       </c>
       <c r="P35">
-        <v>132.6296748882093</v>
+        <v>131.5370714049243</v>
       </c>
       <c r="Q35">
-        <v>313.8296748882094</v>
+        <v>312.7370714049243</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1505826815114096</v>
+        <v>0.1518775769741163</v>
       </c>
       <c r="T35">
-        <v>0.8426128799947531</v>
+        <v>0.853025818272198</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.678444301801663</v>
+        <v>4.540842998807497</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1142978287289276</v>
+        <v>0.1147143768123147</v>
       </c>
       <c r="C36">
-        <v>2828.467885180665</v>
+        <v>2779.645745103072</v>
       </c>
       <c r="D36">
-        <v>3705.583885180665</v>
+        <v>3683.185745103072</v>
       </c>
       <c r="E36">
-        <v>-1628.584</v>
+        <v>-1602.16</v>
       </c>
       <c r="F36">
-        <v>898.4160000000001</v>
+        <v>924.8400000000001</v>
       </c>
       <c r="G36">
         <v>21.3</v>
@@ -4233,45 +4233,45 @@
         <v>225.6</v>
       </c>
       <c r="M36">
-        <v>49.68240480000001</v>
+        <v>53.45575200000001</v>
       </c>
       <c r="N36">
-        <v>175.9175952</v>
+        <v>172.144248</v>
       </c>
       <c r="O36">
-        <v>44.3805237950757</v>
+        <v>43.4285830582421</v>
       </c>
       <c r="P36">
-        <v>131.5370714049243</v>
+        <v>128.7156649417579</v>
       </c>
       <c r="Q36">
-        <v>312.7370714049243</v>
+        <v>309.9156649417579</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1518775769741163</v>
+        <v>0.1532123153741372</v>
       </c>
       <c r="T36">
-        <v>0.853025818272198</v>
+        <v>0.8637591546504874</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.2522801868944358</v>
       </c>
       <c r="W36">
-        <v>0.0413489056647377</v>
+        <v>0.04321820519750161</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.540842998807497</v>
+        <v>4.220312904774026</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1147143768123147</v>
+        <v>0.1144953630545621</v>
       </c>
       <c r="C37">
-        <v>2779.645745103072</v>
+        <v>2764.964435070302</v>
       </c>
       <c r="D37">
-        <v>3683.185745103072</v>
+        <v>3694.928435070302</v>
       </c>
       <c r="E37">
-        <v>-1602.16</v>
+        <v>-1575.736</v>
       </c>
       <c r="F37">
-        <v>924.8400000000001</v>
+        <v>951.2640000000001</v>
       </c>
       <c r="G37">
         <v>21.3</v>
@@ -4315,28 +4315,28 @@
         <v>225.6</v>
       </c>
       <c r="M37">
-        <v>53.45575200000001</v>
+        <v>54.98305920000001</v>
       </c>
       <c r="N37">
-        <v>172.144248</v>
+        <v>170.6169408</v>
       </c>
       <c r="O37">
-        <v>43.4285830582421</v>
+        <v>43.04327371238088</v>
       </c>
       <c r="P37">
-        <v>128.7156649417579</v>
+        <v>127.5736670876191</v>
       </c>
       <c r="Q37">
-        <v>309.9156649417579</v>
+        <v>308.7736670876191</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1532123153741372</v>
+        <v>0.1545887643491586</v>
       </c>
       <c r="T37">
-        <v>0.8637591546504874</v>
+        <v>0.8748279077905982</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.220312904774026</v>
+        <v>4.103081990752525</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1144953630545621</v>
+        <v>0.1152446464547811</v>
       </c>
       <c r="C38">
-        <v>2764.964435070301</v>
+        <v>2698.673452045219</v>
       </c>
       <c r="D38">
-        <v>3694.928435070301</v>
+        <v>3655.061452045219</v>
       </c>
       <c r="E38">
-        <v>-1575.736</v>
+        <v>-1549.312</v>
       </c>
       <c r="F38">
-        <v>951.264</v>
+        <v>977.688</v>
       </c>
       <c r="G38">
         <v>21.3</v>
@@ -4397,45 +4397,45 @@
         <v>225.6</v>
       </c>
       <c r="M38">
-        <v>54.98305920000001</v>
+        <v>59.9322744</v>
       </c>
       <c r="N38">
-        <v>170.6169408</v>
+        <v>165.6677256</v>
       </c>
       <c r="O38">
-        <v>43.04327371238088</v>
+        <v>41.7946847767441</v>
       </c>
       <c r="P38">
-        <v>127.5736670876191</v>
+        <v>123.8730408232559</v>
       </c>
       <c r="Q38">
-        <v>308.7736670876191</v>
+        <v>305.0730408232559</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1545887643491586</v>
+        <v>0.1560089101170379</v>
       </c>
       <c r="T38">
-        <v>0.8748279077905982</v>
+        <v>0.8862480499192839</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.2522801868944358</v>
       </c>
       <c r="W38">
-        <v>0.04321820519750161</v>
+        <v>0.04583522454337109</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.103081990752525</v>
+        <v>3.76424893362632</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1152446464547811</v>
+        <v>0.1150518028904872</v>
       </c>
       <c r="C39">
-        <v>2698.673452045219</v>
+        <v>2682.427599742549</v>
       </c>
       <c r="D39">
-        <v>3655.061452045219</v>
+        <v>3665.239599742549</v>
       </c>
       <c r="E39">
-        <v>-1549.312</v>
+        <v>-1522.888</v>
       </c>
       <c r="F39">
-        <v>977.688</v>
+        <v>1004.112</v>
       </c>
       <c r="G39">
         <v>21.3</v>
@@ -4479,28 +4479,28 @@
         <v>225.6</v>
       </c>
       <c r="M39">
-        <v>59.9322744</v>
+        <v>61.55206560000001</v>
       </c>
       <c r="N39">
-        <v>165.6677256</v>
+        <v>164.0479344</v>
       </c>
       <c r="O39">
-        <v>41.7946847767441</v>
+        <v>41.38604355007813</v>
       </c>
       <c r="P39">
-        <v>123.8730408232559</v>
+        <v>122.6618908499218</v>
       </c>
       <c r="Q39">
-        <v>305.0730408232559</v>
+        <v>303.8618908499218</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1560089101170379</v>
+        <v>0.1574748670387197</v>
       </c>
       <c r="T39">
-        <v>0.8862480499192839</v>
+        <v>0.8980365837295401</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.76424893362632</v>
+        <v>3.665189751162469</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1150518028904872</v>
+        <v>0.1148589593261933</v>
       </c>
       <c r="C40">
-        <v>2682.427599742549</v>
+        <v>2666.238591339613</v>
       </c>
       <c r="D40">
-        <v>3665.239599742549</v>
+        <v>3675.474591339613</v>
       </c>
       <c r="E40">
-        <v>-1522.888</v>
+        <v>-1496.464</v>
       </c>
       <c r="F40">
-        <v>1004.112</v>
+        <v>1030.536</v>
       </c>
       <c r="G40">
         <v>21.3</v>
@@ -4561,28 +4561,28 @@
         <v>225.6</v>
       </c>
       <c r="M40">
-        <v>61.55206560000001</v>
+        <v>63.1718568</v>
       </c>
       <c r="N40">
-        <v>164.0479344</v>
+        <v>162.4281432</v>
       </c>
       <c r="O40">
-        <v>41.38604355007813</v>
+        <v>40.97740232341217</v>
       </c>
       <c r="P40">
-        <v>122.6618908499218</v>
+        <v>121.4507408765878</v>
       </c>
       <c r="Q40">
-        <v>303.8618908499218</v>
+        <v>302.6507408765879</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1574748670387197</v>
+        <v>0.1589888881217681</v>
       </c>
       <c r="T40">
-        <v>0.8980365837295401</v>
+        <v>0.9102116268450509</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.665189751162469</v>
+        <v>3.571210526773688</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1148589593261933</v>
+        <v>0.1155035619525776</v>
       </c>
       <c r="C41">
-        <v>2666.238591339613</v>
+        <v>2605.82464149461</v>
       </c>
       <c r="D41">
-        <v>3675.474591339613</v>
+        <v>3641.48464149461</v>
       </c>
       <c r="E41">
-        <v>-1496.464</v>
+        <v>-1470.04</v>
       </c>
       <c r="F41">
-        <v>1030.536</v>
+        <v>1056.96</v>
       </c>
       <c r="G41">
         <v>21.3</v>
@@ -4643,45 +4643,45 @@
         <v>225.6</v>
       </c>
       <c r="M41">
-        <v>63.1718568</v>
+        <v>67.751136</v>
       </c>
       <c r="N41">
-        <v>162.4281432</v>
+        <v>157.848864</v>
       </c>
       <c r="O41">
-        <v>40.97740232341217</v>
+        <v>39.82214091099437</v>
       </c>
       <c r="P41">
-        <v>121.4507408765878</v>
+        <v>118.0267230890056</v>
       </c>
       <c r="Q41">
-        <v>302.6507408765879</v>
+        <v>299.2267230890056</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1589888881217681</v>
+        <v>0.1605533765742515</v>
       </c>
       <c r="T41">
-        <v>0.9102116268450509</v>
+        <v>0.9227925047310785</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.2522801868944358</v>
       </c>
       <c r="W41">
-        <v>0.04583522454337109</v>
+        <v>0.04792884002006667</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.571210526773688</v>
+        <v>3.329833465818197</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1155035619525776</v>
+        <v>0.1153316545430506</v>
       </c>
       <c r="C42">
-        <v>2605.82464149461</v>
+        <v>2588.403709171706</v>
       </c>
       <c r="D42">
-        <v>3641.48464149461</v>
+        <v>3650.487709171706</v>
       </c>
       <c r="E42">
-        <v>-1470.04</v>
+        <v>-1443.616</v>
       </c>
       <c r="F42">
-        <v>1056.96</v>
+        <v>1083.384</v>
       </c>
       <c r="G42">
         <v>21.3</v>
@@ -4725,28 +4725,28 @@
         <v>225.6</v>
       </c>
       <c r="M42">
-        <v>67.751136</v>
+        <v>69.4449144</v>
       </c>
       <c r="N42">
-        <v>157.848864</v>
+        <v>156.1550856</v>
       </c>
       <c r="O42">
-        <v>39.82214091099437</v>
+        <v>39.39483417968462</v>
       </c>
       <c r="P42">
-        <v>118.0267230890056</v>
+        <v>116.7602514203154</v>
       </c>
       <c r="Q42">
-        <v>299.2267230890056</v>
+        <v>297.9602514203154</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1605533765742515</v>
+        <v>0.1621708985335988</v>
       </c>
       <c r="T42">
-        <v>0.9227925047310785</v>
+        <v>0.9357998530539207</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.329833465818197</v>
+        <v>3.248618015432387</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1153316545430506</v>
+        <v>0.1151597471335236</v>
       </c>
       <c r="C43">
-        <v>2588.403709171706</v>
+        <v>2571.02740486739</v>
       </c>
       <c r="D43">
-        <v>3650.487709171706</v>
+        <v>3659.53540486739</v>
       </c>
       <c r="E43">
-        <v>-1443.616</v>
+        <v>-1417.192</v>
       </c>
       <c r="F43">
-        <v>1083.384</v>
+        <v>1109.808</v>
       </c>
       <c r="G43">
         <v>21.3</v>
@@ -4807,28 +4807,28 @@
         <v>225.6</v>
       </c>
       <c r="M43">
-        <v>69.4449144</v>
+        <v>71.13869280000002</v>
       </c>
       <c r="N43">
-        <v>156.1550856</v>
+        <v>154.4613072</v>
       </c>
       <c r="O43">
-        <v>39.39483417968462</v>
+        <v>38.96752744837485</v>
       </c>
       <c r="P43">
-        <v>116.7602514203154</v>
+        <v>115.4937797516251</v>
       </c>
       <c r="Q43">
-        <v>297.9602514203154</v>
+        <v>296.6937797516251</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1621708985335988</v>
+        <v>0.1638441971122339</v>
       </c>
       <c r="T43">
-        <v>0.9357998530539207</v>
+        <v>0.9492557306292746</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.248618015432387</v>
+        <v>3.171269967445901</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1151597471335236</v>
+        <v>0.1149878397239967</v>
       </c>
       <c r="C44">
-        <v>2571.027404867391</v>
+        <v>2553.69606123638</v>
       </c>
       <c r="D44">
-        <v>3659.535404867391</v>
+        <v>3668.628061236379</v>
       </c>
       <c r="E44">
-        <v>-1417.192</v>
+        <v>-1390.768</v>
       </c>
       <c r="F44">
-        <v>1109.808</v>
+        <v>1136.232</v>
       </c>
       <c r="G44">
         <v>21.3</v>
@@ -4889,28 +4889,28 @@
         <v>225.6</v>
       </c>
       <c r="M44">
-        <v>71.1386928</v>
+        <v>72.8324712</v>
       </c>
       <c r="N44">
-        <v>154.4613072</v>
+        <v>152.7675288</v>
       </c>
       <c r="O44">
-        <v>38.96752744837485</v>
+        <v>38.54022071706509</v>
       </c>
       <c r="P44">
-        <v>115.4937797516251</v>
+        <v>114.2273080829349</v>
       </c>
       <c r="Q44">
-        <v>296.6937797516251</v>
+        <v>295.4273080829349</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1638441971122338</v>
+        <v>0.1655762079216982</v>
       </c>
       <c r="T44">
-        <v>0.9492557306292744</v>
+        <v>0.9631837442599041</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.171269967445902</v>
+        <v>3.097519503086694</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1149878397239967</v>
+        <v>0.1148159323144697</v>
       </c>
       <c r="C45">
-        <v>2553.69606123638</v>
+        <v>2536.410014247745</v>
       </c>
       <c r="D45">
-        <v>3668.628061236379</v>
+        <v>3677.766014247744</v>
       </c>
       <c r="E45">
-        <v>-1390.768</v>
+        <v>-1364.344</v>
       </c>
       <c r="F45">
-        <v>1136.232</v>
+        <v>1162.656</v>
       </c>
       <c r="G45">
         <v>21.3</v>
@@ -4971,28 +4971,28 @@
         <v>225.6</v>
       </c>
       <c r="M45">
-        <v>72.8324712</v>
+        <v>74.5262496</v>
       </c>
       <c r="N45">
-        <v>152.7675288</v>
+        <v>151.0737504</v>
       </c>
       <c r="O45">
-        <v>38.54022071706509</v>
+        <v>38.11291398575534</v>
       </c>
       <c r="P45">
-        <v>114.2273080829349</v>
+        <v>112.9608364142447</v>
       </c>
       <c r="Q45">
-        <v>295.4273080829349</v>
+        <v>294.1608364142447</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1655762079216982</v>
+        <v>0.1673700762600721</v>
       </c>
       <c r="T45">
-        <v>0.9631837442599041</v>
+        <v>0.9776091869487703</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.097519503086694</v>
+        <v>3.027121332561997</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1148159323144697</v>
+        <v>0.1172685214489432</v>
       </c>
       <c r="C46">
-        <v>2536.410014247745</v>
+        <v>2383.775918071009</v>
       </c>
       <c r="D46">
-        <v>3677.766014247744</v>
+        <v>3551.555918071009</v>
       </c>
       <c r="E46">
-        <v>-1364.344</v>
+        <v>-1337.92</v>
       </c>
       <c r="F46">
-        <v>1162.656</v>
+        <v>1189.08</v>
       </c>
       <c r="G46">
         <v>21.3</v>
@@ -5053,45 +5053,45 @@
         <v>225.6</v>
       </c>
       <c r="M46">
-        <v>74.5262496</v>
+        <v>85.49485200000002</v>
       </c>
       <c r="N46">
-        <v>151.0737504</v>
+        <v>140.105148</v>
       </c>
       <c r="O46">
-        <v>38.11291398575534</v>
+        <v>35.34575292231258</v>
       </c>
       <c r="P46">
-        <v>112.9608364142447</v>
+        <v>104.7593950776874</v>
       </c>
       <c r="Q46">
-        <v>294.1608364142447</v>
+        <v>285.9593950776874</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1673700762600721</v>
+        <v>0.1692291761743867</v>
       </c>
       <c r="T46">
-        <v>0.9776091869487703</v>
+        <v>0.9925591911899589</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.2522801868944358</v>
       </c>
       <c r="W46">
-        <v>0.04792884002006667</v>
+        <v>0.05376105456229007</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.027121332561997</v>
+        <v>2.638755372077841</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1172685214489432</v>
+        <v>0.1171549361848385</v>
       </c>
       <c r="C47">
-        <v>2383.775918071009</v>
+        <v>2363.005408053705</v>
       </c>
       <c r="D47">
-        <v>3551.555918071009</v>
+        <v>3557.209408053704</v>
       </c>
       <c r="E47">
-        <v>-1337.92</v>
+        <v>-1311.496</v>
       </c>
       <c r="F47">
-        <v>1189.08</v>
+        <v>1215.504</v>
       </c>
       <c r="G47">
         <v>21.3</v>
@@ -5135,28 +5135,28 @@
         <v>225.6</v>
       </c>
       <c r="M47">
-        <v>85.49485200000002</v>
+        <v>87.39473760000001</v>
       </c>
       <c r="N47">
-        <v>140.105148</v>
+        <v>138.2052624</v>
       </c>
       <c r="O47">
-        <v>35.34575292231258</v>
+        <v>34.86644942806653</v>
       </c>
       <c r="P47">
-        <v>104.7593950776874</v>
+        <v>103.3388129719335</v>
       </c>
       <c r="Q47">
-        <v>285.9593950776874</v>
+        <v>284.5388129719335</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1692291761743867</v>
+        <v>0.1711571316410835</v>
       </c>
       <c r="T47">
-        <v>0.9925591911899589</v>
+        <v>1.008062899291932</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.638755372077841</v>
+        <v>2.581391124858758</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1171549361848385</v>
+        <v>0.1170413509207338</v>
       </c>
       <c r="C48">
-        <v>2363.005408053705</v>
+        <v>2342.252925576431</v>
       </c>
       <c r="D48">
-        <v>3557.209408053704</v>
+        <v>3562.880925576431</v>
       </c>
       <c r="E48">
-        <v>-1311.496</v>
+        <v>-1285.072</v>
       </c>
       <c r="F48">
-        <v>1215.504</v>
+        <v>1241.928</v>
       </c>
       <c r="G48">
         <v>21.3</v>
@@ -5217,28 +5217,28 @@
         <v>225.6</v>
       </c>
       <c r="M48">
-        <v>87.39473760000001</v>
+        <v>89.29462320000002</v>
       </c>
       <c r="N48">
-        <v>138.2052624</v>
+        <v>136.3053768</v>
       </c>
       <c r="O48">
-        <v>34.86644942806653</v>
+        <v>34.38714593382048</v>
       </c>
       <c r="P48">
-        <v>103.3388129719335</v>
+        <v>101.9182308661795</v>
       </c>
       <c r="Q48">
-        <v>284.5388129719335</v>
+        <v>283.1182308661795</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1711571316410835</v>
+        <v>0.1731578401442593</v>
       </c>
       <c r="T48">
-        <v>1.008062899291932</v>
+        <v>1.02415165298266</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.581391124858758</v>
+        <v>2.526467909436231</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1170413509207338</v>
+        <v>0.1183274971467626</v>
       </c>
       <c r="C49">
-        <v>2342.252925576431</v>
+        <v>2252.647566278348</v>
       </c>
       <c r="D49">
-        <v>3562.880925576431</v>
+        <v>3499.699566278347</v>
       </c>
       <c r="E49">
-        <v>-1285.072</v>
+        <v>-1258.648</v>
       </c>
       <c r="F49">
-        <v>1241.928</v>
+        <v>1268.352</v>
       </c>
       <c r="G49">
         <v>21.3</v>
@@ -5299,45 +5299,45 @@
         <v>225.6</v>
       </c>
       <c r="M49">
-        <v>89.29462320000002</v>
+        <v>96.14108160000002</v>
       </c>
       <c r="N49">
-        <v>136.3053768</v>
+        <v>129.4589184</v>
       </c>
       <c r="O49">
-        <v>34.38714593382048</v>
+        <v>32.6599201291035</v>
       </c>
       <c r="P49">
-        <v>101.9182308661795</v>
+        <v>96.79899827089646</v>
       </c>
       <c r="Q49">
-        <v>283.1182308661795</v>
+        <v>277.9989982708965</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1731578401442593</v>
+        <v>0.1752354989744803</v>
       </c>
       <c r="T49">
-        <v>1.02415165298266</v>
+        <v>1.040859204892261</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.2522801868944358</v>
       </c>
       <c r="W49">
-        <v>0.05376105456229007</v>
+        <v>0.05667716183340177</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.526467909436231</v>
+        <v>2.346551507903984</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1183274971467626</v>
+        <v>0.118243072955369</v>
       </c>
       <c r="C50">
-        <v>2252.647566278348</v>
+        <v>2230.302069494048</v>
       </c>
       <c r="D50">
-        <v>3499.699566278347</v>
+        <v>3503.778069494047</v>
       </c>
       <c r="E50">
-        <v>-1258.648</v>
+        <v>-1232.224</v>
       </c>
       <c r="F50">
-        <v>1268.352</v>
+        <v>1294.776</v>
       </c>
       <c r="G50">
         <v>21.3</v>
@@ -5381,28 +5381,28 @@
         <v>225.6</v>
       </c>
       <c r="M50">
-        <v>96.14108160000002</v>
+        <v>98.14402080000001</v>
       </c>
       <c r="N50">
-        <v>129.4589184</v>
+        <v>127.4559792</v>
       </c>
       <c r="O50">
-        <v>32.6599201291035</v>
+        <v>32.15461825338932</v>
       </c>
       <c r="P50">
-        <v>96.79899827089646</v>
+        <v>95.30136094661067</v>
       </c>
       <c r="Q50">
-        <v>277.9989982708965</v>
+        <v>276.5013609466107</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1752354989744803</v>
+        <v>0.1773946346215728</v>
       </c>
       <c r="T50">
-        <v>1.040859204892261</v>
+        <v>1.058221954915964</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.346551507903984</v>
+        <v>2.298662701620229</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.118243072955369</v>
+        <v>0.1181586487639754</v>
       </c>
       <c r="C51">
-        <v>2230.302069494048</v>
+        <v>2207.966089867462</v>
       </c>
       <c r="D51">
-        <v>3503.778069494047</v>
+        <v>3507.866089867462</v>
       </c>
       <c r="E51">
-        <v>-1232.224</v>
+        <v>-1205.8</v>
       </c>
       <c r="F51">
-        <v>1294.776</v>
+        <v>1321.2</v>
       </c>
       <c r="G51">
         <v>21.3</v>
@@ -5463,28 +5463,28 @@
         <v>225.6</v>
       </c>
       <c r="M51">
-        <v>98.14402080000001</v>
+        <v>100.14696</v>
       </c>
       <c r="N51">
-        <v>127.4559792</v>
+        <v>125.45304</v>
       </c>
       <c r="O51">
-        <v>32.15461825338932</v>
+        <v>31.64931637767512</v>
       </c>
       <c r="P51">
-        <v>95.30136094661067</v>
+        <v>93.80372362232487</v>
       </c>
       <c r="Q51">
-        <v>276.5013609466107</v>
+        <v>275.0037236223249</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1773946346215728</v>
+        <v>0.179640135694549</v>
       </c>
       <c r="T51">
-        <v>1.058221954915964</v>
+        <v>1.076279214940616</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.298662701620229</v>
+        <v>2.252689447587825</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1181586487639754</v>
+        <v>0.1180742245725817</v>
       </c>
       <c r="C52">
-        <v>2207.966089867462</v>
+        <v>2185.639660749827</v>
       </c>
       <c r="D52">
-        <v>3507.866089867462</v>
+        <v>3511.963660749827</v>
       </c>
       <c r="E52">
-        <v>-1205.8</v>
+        <v>-1179.376</v>
       </c>
       <c r="F52">
-        <v>1321.2</v>
+        <v>1347.624</v>
       </c>
       <c r="G52">
         <v>21.3</v>
@@ -5545,28 +5545,28 @@
         <v>225.6</v>
       </c>
       <c r="M52">
-        <v>100.14696</v>
+        <v>102.1498992</v>
       </c>
       <c r="N52">
-        <v>125.45304</v>
+        <v>123.4501008</v>
       </c>
       <c r="O52">
-        <v>31.64931637767512</v>
+        <v>31.14401450196093</v>
       </c>
       <c r="P52">
-        <v>93.80372362232487</v>
+        <v>92.30608629803905</v>
       </c>
       <c r="Q52">
-        <v>275.0037236223249</v>
+        <v>273.5060862980391</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.179640135694549</v>
+        <v>0.1819772898725446</v>
       </c>
       <c r="T52">
-        <v>1.076279214940616</v>
+        <v>1.095073505986681</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.252689447587825</v>
+        <v>2.208519066262573</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1180742245725817</v>
+        <v>0.1179898003811881</v>
       </c>
       <c r="C53">
-        <v>2185.639660749827</v>
+        <v>2163.3228156484</v>
       </c>
       <c r="D53">
-        <v>3511.963660749827</v>
+        <v>3516.0708156484</v>
       </c>
       <c r="E53">
-        <v>-1179.376</v>
+        <v>-1152.952</v>
       </c>
       <c r="F53">
-        <v>1347.624</v>
+        <v>1374.048</v>
       </c>
       <c r="G53">
         <v>21.3</v>
@@ -5627,28 +5627,28 @@
         <v>225.6</v>
       </c>
       <c r="M53">
-        <v>102.1498992</v>
+        <v>104.1528384</v>
       </c>
       <c r="N53">
-        <v>123.4501008</v>
+        <v>121.4471616</v>
       </c>
       <c r="O53">
-        <v>31.14401450196093</v>
+        <v>30.63871262624674</v>
       </c>
       <c r="P53">
-        <v>92.30608629803905</v>
+        <v>90.80844897375324</v>
       </c>
       <c r="Q53">
-        <v>273.5060862980391</v>
+        <v>272.0084489737533</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1819772898725446</v>
+        <v>0.1844118254746233</v>
       </c>
       <c r="T53">
-        <v>1.095073505986681</v>
+        <v>1.114650892493</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.208519066262573</v>
+        <v>2.166047545757523</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1179898003811881</v>
+        <v>0.1179053761897945</v>
       </c>
       <c r="C54">
-        <v>2163.3228156484</v>
+        <v>2141.015588227361</v>
       </c>
       <c r="D54">
-        <v>3516.0708156484</v>
+        <v>3520.187588227361</v>
       </c>
       <c r="E54">
-        <v>-1152.952</v>
+        <v>-1126.528</v>
       </c>
       <c r="F54">
-        <v>1374.048</v>
+        <v>1400.472</v>
       </c>
       <c r="G54">
         <v>21.3</v>
@@ -5709,28 +5709,28 @@
         <v>225.6</v>
       </c>
       <c r="M54">
-        <v>104.1528384</v>
+        <v>106.1557776</v>
       </c>
       <c r="N54">
-        <v>121.4471616</v>
+        <v>119.4442224</v>
       </c>
       <c r="O54">
-        <v>30.63871262624674</v>
+        <v>30.13341075053254</v>
       </c>
       <c r="P54">
-        <v>90.80844897375324</v>
+        <v>89.31081164946742</v>
       </c>
       <c r="Q54">
-        <v>272.0084489737533</v>
+        <v>270.5108116494674</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1844118254746233</v>
+        <v>0.186949958336365</v>
       </c>
       <c r="T54">
-        <v>1.114650892493</v>
+        <v>1.135061359276183</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.166047545757523</v>
+        <v>2.125178724139457</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1179053761897945</v>
+        <v>0.1178209519984009</v>
       </c>
       <c r="C55">
-        <v>2141.015588227361</v>
+        <v>2118.718012308738</v>
       </c>
       <c r="D55">
-        <v>3520.187588227361</v>
+        <v>3524.314012308738</v>
       </c>
       <c r="E55">
-        <v>-1126.528</v>
+        <v>-1100.104</v>
       </c>
       <c r="F55">
-        <v>1400.472</v>
+        <v>1426.896</v>
       </c>
       <c r="G55">
         <v>21.3</v>
@@ -5791,28 +5791,28 @@
         <v>225.6</v>
       </c>
       <c r="M55">
-        <v>106.1557776</v>
+        <v>108.1587168</v>
       </c>
       <c r="N55">
-        <v>119.4442224</v>
+        <v>117.4412832</v>
       </c>
       <c r="O55">
-        <v>30.13341075053254</v>
+        <v>29.62810887481835</v>
       </c>
       <c r="P55">
-        <v>89.31081164946742</v>
+        <v>87.81317432518162</v>
       </c>
       <c r="Q55">
-        <v>270.5108116494674</v>
+        <v>269.0131743251816</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.186949958336365</v>
+        <v>0.1895984448007911</v>
       </c>
       <c r="T55">
-        <v>1.135061359276183</v>
+        <v>1.156359237658635</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.125178724139457</v>
+        <v>2.085823562581319</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1178209519984009</v>
+        <v>0.1177365278070073</v>
       </c>
       <c r="C56">
-        <v>2118.718012308738</v>
+        <v>2096.430121873334</v>
       </c>
       <c r="D56">
-        <v>3524.314012308738</v>
+        <v>3528.450121873334</v>
       </c>
       <c r="E56">
-        <v>-1100.104</v>
+        <v>-1073.68</v>
       </c>
       <c r="F56">
-        <v>1426.896</v>
+        <v>1453.32</v>
       </c>
       <c r="G56">
         <v>21.3</v>
@@ -5873,28 +5873,28 @@
         <v>225.6</v>
       </c>
       <c r="M56">
-        <v>108.1587168</v>
+        <v>110.161656</v>
       </c>
       <c r="N56">
-        <v>117.4412832</v>
+        <v>115.438344</v>
       </c>
       <c r="O56">
-        <v>29.62810887481835</v>
+        <v>29.12280699910416</v>
       </c>
       <c r="P56">
-        <v>87.81317432518162</v>
+        <v>86.31553700089582</v>
       </c>
       <c r="Q56">
-        <v>269.0131743251816</v>
+        <v>267.5155370008958</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1895984448007911</v>
+        <v>0.1923646417747473</v>
       </c>
       <c r="T56">
-        <v>1.156359237658635</v>
+        <v>1.178603688413641</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.085823562581319</v>
+        <v>2.047899497807113</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1177365278070073</v>
+        <v>0.1176521036156136</v>
       </c>
       <c r="C57">
-        <v>2096.430121873334</v>
+        <v>2074.151951061656</v>
       </c>
       <c r="D57">
-        <v>3528.450121873334</v>
+        <v>3532.595951061656</v>
       </c>
       <c r="E57">
-        <v>-1073.68</v>
+        <v>-1047.256</v>
       </c>
       <c r="F57">
-        <v>1453.32</v>
+        <v>1479.744</v>
       </c>
       <c r="G57">
         <v>21.3</v>
@@ -5955,28 +5955,28 @@
         <v>225.6</v>
       </c>
       <c r="M57">
-        <v>110.161656</v>
+        <v>112.1645952</v>
       </c>
       <c r="N57">
-        <v>115.438344</v>
+        <v>113.4354048</v>
       </c>
       <c r="O57">
-        <v>29.12280699910416</v>
+        <v>28.61750512338997</v>
       </c>
       <c r="P57">
-        <v>86.31553700089582</v>
+        <v>84.81789967661001</v>
       </c>
       <c r="Q57">
-        <v>267.5155370008958</v>
+        <v>266.01789967661</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1923646417747473</v>
+        <v>0.1952565749747923</v>
       </c>
       <c r="T57">
-        <v>1.178603688413641</v>
+        <v>1.201859250566601</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.047899497807113</v>
+        <v>2.0113298639177</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1176521036156136</v>
+        <v>0.1236197235914964</v>
       </c>
       <c r="C58">
-        <v>2074.151951061656</v>
+        <v>1776.8301735915</v>
       </c>
       <c r="D58">
-        <v>3532.595951061656</v>
+        <v>3261.6981735915</v>
       </c>
       <c r="E58">
-        <v>-1047.256</v>
+        <v>-1020.832</v>
       </c>
       <c r="F58">
-        <v>1479.744</v>
+        <v>1506.168</v>
       </c>
       <c r="G58">
         <v>21.3</v>
@@ -6037,45 +6037,45 @@
         <v>225.6</v>
       </c>
       <c r="M58">
-        <v>112.1645952</v>
+        <v>135.55512</v>
       </c>
       <c r="N58">
-        <v>113.4354048</v>
+        <v>90.04487999999998</v>
       </c>
       <c r="O58">
-        <v>28.61750512338997</v>
+        <v>22.71653915528703</v>
       </c>
       <c r="P58">
-        <v>84.81789967661001</v>
+        <v>67.32834084471294</v>
       </c>
       <c r="Q58">
-        <v>266.01789967661</v>
+        <v>248.5283408447129</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1952565749747923</v>
+        <v>0.1982830166957698</v>
       </c>
       <c r="T58">
-        <v>1.201859250566601</v>
+        <v>1.226196466773187</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.2522801868944358</v>
       </c>
       <c r="W58">
-        <v>0.05667716183340177</v>
+        <v>0.06729478317950077</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.0113298639177</v>
+        <v>1.664267642564884</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1236197235914964</v>
+        <v>0.1236414756135638</v>
       </c>
       <c r="C59">
-        <v>1776.8301735915</v>
+        <v>1749.494724648762</v>
       </c>
       <c r="D59">
-        <v>3261.6981735915</v>
+        <v>3260.786724648763</v>
       </c>
       <c r="E59">
-        <v>-1020.832</v>
+        <v>-994.4079999999997</v>
       </c>
       <c r="F59">
-        <v>1506.168</v>
+        <v>1532.592</v>
       </c>
       <c r="G59">
         <v>21.3</v>
@@ -6119,28 +6119,28 @@
         <v>225.6</v>
       </c>
       <c r="M59">
-        <v>135.55512</v>
+        <v>137.93328</v>
       </c>
       <c r="N59">
-        <v>90.04487999999998</v>
+        <v>87.66671999999997</v>
       </c>
       <c r="O59">
-        <v>22.71653915528703</v>
+        <v>22.11657650602216</v>
       </c>
       <c r="P59">
-        <v>67.32834084471294</v>
+        <v>65.5501434939778</v>
       </c>
       <c r="Q59">
-        <v>248.5283408447129</v>
+        <v>246.7501434939778</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1982830166957698</v>
+        <v>0.2014535746891747</v>
       </c>
       <c r="T59">
-        <v>1.226196466773187</v>
+        <v>1.25169259803723</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.664267642564884</v>
+        <v>1.63557337286549</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1236414756135638</v>
+        <v>0.1236632276356312</v>
       </c>
       <c r="C60">
-        <v>1749.494724648764</v>
+        <v>1722.15978495431</v>
       </c>
       <c r="D60">
-        <v>3260.786724648764</v>
+        <v>3259.87578495431</v>
       </c>
       <c r="E60">
-        <v>-994.4080000000001</v>
+        <v>-967.9839999999999</v>
       </c>
       <c r="F60">
-        <v>1532.592</v>
+        <v>1559.016</v>
       </c>
       <c r="G60">
         <v>21.3</v>
@@ -6201,28 +6201,28 @@
         <v>225.6</v>
       </c>
       <c r="M60">
-        <v>137.93328</v>
+        <v>140.31144</v>
       </c>
       <c r="N60">
-        <v>87.66672</v>
+        <v>85.28855999999999</v>
       </c>
       <c r="O60">
-        <v>22.11657650602217</v>
+        <v>21.5166138567573</v>
       </c>
       <c r="P60">
-        <v>65.55014349397783</v>
+        <v>63.77194614324269</v>
       </c>
       <c r="Q60">
-        <v>246.7501434939778</v>
+        <v>244.9719461432427</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2014535746891746</v>
+        <v>0.2047787940481115</v>
       </c>
       <c r="T60">
-        <v>1.25169259803723</v>
+        <v>1.27843244302147</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.63557337286549</v>
+        <v>1.607851790274549</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1236632276356312</v>
+        <v>0.1236849796576985</v>
       </c>
       <c r="C61">
-        <v>1722.15978495431</v>
+        <v>1694.825354081467</v>
       </c>
       <c r="D61">
-        <v>3259.87578495431</v>
+        <v>3258.965354081467</v>
       </c>
       <c r="E61">
-        <v>-967.9839999999999</v>
+        <v>-941.5599999999999</v>
       </c>
       <c r="F61">
-        <v>1559.016</v>
+        <v>1585.44</v>
       </c>
       <c r="G61">
         <v>21.3</v>
@@ -6283,28 +6283,28 @@
         <v>225.6</v>
       </c>
       <c r="M61">
-        <v>140.31144</v>
+        <v>142.6896</v>
       </c>
       <c r="N61">
-        <v>85.28855999999999</v>
+        <v>82.91039999999998</v>
       </c>
       <c r="O61">
-        <v>21.5166138567573</v>
+        <v>20.91665120749242</v>
       </c>
       <c r="P61">
-        <v>63.77194614324269</v>
+        <v>61.99374879250756</v>
       </c>
       <c r="Q61">
-        <v>244.9719461432427</v>
+        <v>243.1937487925076</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2047787940481115</v>
+        <v>0.2082702743749951</v>
       </c>
       <c r="T61">
-        <v>1.27843244302147</v>
+        <v>1.306509280254921</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.607851790274549</v>
+        <v>1.58105426043664</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1236849796576985</v>
+        <v>0.1237067316797659</v>
       </c>
       <c r="C62">
-        <v>1694.825354081467</v>
+        <v>1667.491431604034</v>
       </c>
       <c r="D62">
-        <v>3258.965354081467</v>
+        <v>3258.055431604033</v>
       </c>
       <c r="E62">
-        <v>-941.5599999999999</v>
+        <v>-915.136</v>
       </c>
       <c r="F62">
-        <v>1585.44</v>
+        <v>1611.864</v>
       </c>
       <c r="G62">
         <v>21.3</v>
@@ -6365,28 +6365,28 @@
         <v>225.6</v>
       </c>
       <c r="M62">
-        <v>142.6896</v>
+        <v>145.06776</v>
       </c>
       <c r="N62">
-        <v>82.91039999999998</v>
+        <v>80.53224</v>
       </c>
       <c r="O62">
-        <v>20.91665120749242</v>
+        <v>20.31668855822756</v>
       </c>
       <c r="P62">
-        <v>61.99374879250756</v>
+        <v>60.21555144177245</v>
       </c>
       <c r="Q62">
-        <v>243.1937487925076</v>
+        <v>241.4155514417725</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2082702743749951</v>
+        <v>0.2119408049750524</v>
       </c>
       <c r="T62">
-        <v>1.306509280254921</v>
+        <v>1.336025955295217</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.58105426043664</v>
+        <v>1.5551353381344</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1237067316797659</v>
+        <v>0.1237284837018333</v>
       </c>
       <c r="C63">
-        <v>1667.491431604034</v>
+        <v>1640.158017096289</v>
       </c>
       <c r="D63">
-        <v>3258.055431604033</v>
+        <v>3257.146017096289</v>
       </c>
       <c r="E63">
-        <v>-915.136</v>
+        <v>-888.712</v>
       </c>
       <c r="F63">
-        <v>1611.864</v>
+        <v>1638.288</v>
       </c>
       <c r="G63">
         <v>21.3</v>
@@ -6447,28 +6447,28 @@
         <v>225.6</v>
       </c>
       <c r="M63">
-        <v>145.06776</v>
+        <v>147.44592</v>
       </c>
       <c r="N63">
-        <v>80.53224</v>
+        <v>78.15407999999999</v>
       </c>
       <c r="O63">
-        <v>20.31668855822756</v>
+        <v>19.71672590896268</v>
       </c>
       <c r="P63">
-        <v>60.21555144177245</v>
+        <v>58.43735409103731</v>
       </c>
       <c r="Q63">
-        <v>241.4155514417725</v>
+        <v>239.6373540910373</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2119408049750524</v>
+        <v>0.2158045213961652</v>
       </c>
       <c r="T63">
-        <v>1.336025955295217</v>
+        <v>1.36709613954816</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.5551353381344</v>
+        <v>1.530052510099974</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1237284837018333</v>
+        <v>0.1237502357239006</v>
       </c>
       <c r="C64">
-        <v>1640.158017096289</v>
+        <v>1612.825110132987</v>
       </c>
       <c r="D64">
-        <v>3257.146017096289</v>
+        <v>3256.237110132987</v>
       </c>
       <c r="E64">
-        <v>-888.712</v>
+        <v>-862.288</v>
       </c>
       <c r="F64">
-        <v>1638.288</v>
+        <v>1664.712</v>
       </c>
       <c r="G64">
         <v>21.3</v>
@@ -6529,28 +6529,28 @@
         <v>225.6</v>
       </c>
       <c r="M64">
-        <v>147.44592</v>
+        <v>149.82408</v>
       </c>
       <c r="N64">
-        <v>78.15407999999999</v>
+        <v>75.77592000000001</v>
       </c>
       <c r="O64">
-        <v>19.71672590896268</v>
+        <v>19.11676325969782</v>
       </c>
       <c r="P64">
-        <v>58.43735409103731</v>
+        <v>56.65915674030219</v>
       </c>
       <c r="Q64">
-        <v>239.6373540910373</v>
+        <v>237.8591567403022</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2158045213961652</v>
+        <v>0.2198770873535544</v>
       </c>
       <c r="T64">
-        <v>1.36709613954816</v>
+        <v>1.39984579322018</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.530052510099974</v>
+        <v>1.50576596232061</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1237502357239006</v>
+        <v>0.1542449387879282</v>
       </c>
       <c r="C65">
-        <v>1612.825110132987</v>
+        <v>670.747646823306</v>
       </c>
       <c r="D65">
-        <v>3256.237110132987</v>
+        <v>2340.583646823306</v>
       </c>
       <c r="E65">
-        <v>-862.288</v>
+        <v>-835.8639999999998</v>
       </c>
       <c r="F65">
-        <v>1664.712</v>
+        <v>1691.136</v>
       </c>
       <c r="G65">
         <v>21.3</v>
@@ -6611,45 +6611,45 @@
         <v>225.6</v>
       </c>
       <c r="M65">
-        <v>149.82408</v>
+        <v>248.2587648000001</v>
       </c>
       <c r="N65">
-        <v>75.77592000000001</v>
+        <v>-22.65876480000006</v>
       </c>
       <c r="O65">
-        <v>19.11676325969782</v>
+        <v>-5.716357418541077</v>
       </c>
       <c r="P65">
-        <v>56.65915674030219</v>
+        <v>-16.94240738145898</v>
       </c>
       <c r="Q65">
-        <v>237.8591567403022</v>
+        <v>164.257592618541</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2198770873535544</v>
+        <v>0.2273106851690027</v>
       </c>
       <c r="T65">
-        <v>1.39984579322018</v>
+        <v>1.459623279095225</v>
       </c>
       <c r="U65">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2522801868944358</v>
+        <v>0.2292543838653011</v>
       </c>
       <c r="W65">
-        <v>0.06729478317950077</v>
+        <v>0.1131454564485738</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.50576596232061</v>
+        <v>0.9087292453974215</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1542449387879282</v>
+        <v>0.1552549387879282</v>
       </c>
       <c r="C66">
-        <v>670.747646823306</v>
+        <v>622.725813875157</v>
       </c>
       <c r="D66">
-        <v>2340.583646823306</v>
+        <v>2318.985813875157</v>
       </c>
       <c r="E66">
-        <v>-835.8639999999998</v>
+        <v>-809.4399999999998</v>
       </c>
       <c r="F66">
-        <v>1691.136</v>
+        <v>1717.56</v>
       </c>
       <c r="G66">
         <v>21.3</v>
@@ -6693,37 +6693,37 @@
         <v>225.6</v>
       </c>
       <c r="M66">
-        <v>248.2587648000001</v>
+        <v>252.137808</v>
       </c>
       <c r="N66">
-        <v>-22.65876480000006</v>
+        <v>-26.53780800000004</v>
       </c>
       <c r="O66">
-        <v>-5.716357418541077</v>
+        <v>-6.694963162008663</v>
       </c>
       <c r="P66">
-        <v>-16.94240738145898</v>
+        <v>-19.84284483799138</v>
       </c>
       <c r="Q66">
-        <v>164.257592618541</v>
+        <v>161.3571551620086</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2273106851690027</v>
+        <v>0.2324967047452599</v>
       </c>
       <c r="T66">
-        <v>1.459623279095225</v>
+        <v>1.501326801355089</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2292543838653011</v>
+        <v>0.2257273933442965</v>
       </c>
       <c r="W66">
-        <v>0.1131454564485738</v>
+        <v>0.1136632186570573</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9087292453974215</v>
+        <v>0.8947487954682305</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1552549387879282</v>
+        <v>0.1562649387879282</v>
       </c>
       <c r="C67">
-        <v>622.725813875157</v>
+        <v>575.0989263552503</v>
       </c>
       <c r="D67">
-        <v>2318.985813875157</v>
+        <v>2297.78292635525</v>
       </c>
       <c r="E67">
-        <v>-809.4399999999998</v>
+        <v>-783.0159999999998</v>
       </c>
       <c r="F67">
-        <v>1717.56</v>
+        <v>1743.984</v>
       </c>
       <c r="G67">
         <v>21.3</v>
@@ -6775,37 +6775,37 @@
         <v>225.6</v>
       </c>
       <c r="M67">
-        <v>252.137808</v>
+        <v>256.0168512</v>
       </c>
       <c r="N67">
-        <v>-26.53780800000004</v>
+        <v>-30.41685120000002</v>
       </c>
       <c r="O67">
-        <v>-6.694963162008663</v>
+        <v>-7.673568905476249</v>
       </c>
       <c r="P67">
-        <v>-19.84284483799138</v>
+        <v>-22.74328229452378</v>
       </c>
       <c r="Q67">
-        <v>161.3571551620086</v>
+        <v>158.4567177054763</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2324967047452599</v>
+        <v>0.2379877842965911</v>
       </c>
       <c r="T67">
-        <v>1.501326801355089</v>
+        <v>1.545483471983179</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2257273933442965</v>
+        <v>0.2223072813239283</v>
       </c>
       <c r="W67">
-        <v>0.1136632186570573</v>
+        <v>0.1141652911016473</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8947487954682305</v>
+        <v>0.8811919955368936</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1562649387879282</v>
+        <v>0.1572749387879282</v>
       </c>
       <c r="C68">
-        <v>575.0989263552503</v>
+        <v>527.8562492530016</v>
       </c>
       <c r="D68">
-        <v>2297.78292635525</v>
+        <v>2276.964249253002</v>
       </c>
       <c r="E68">
-        <v>-783.0159999999998</v>
+        <v>-756.5919999999999</v>
       </c>
       <c r="F68">
-        <v>1743.984</v>
+        <v>1770.408</v>
       </c>
       <c r="G68">
         <v>21.3</v>
@@ -6857,37 +6857,37 @@
         <v>225.6</v>
       </c>
       <c r="M68">
-        <v>256.0168512</v>
+        <v>259.8958944</v>
       </c>
       <c r="N68">
-        <v>-30.41685120000002</v>
+        <v>-34.29589440000004</v>
       </c>
       <c r="O68">
-        <v>-7.673568905476249</v>
+        <v>-8.652174648943843</v>
       </c>
       <c r="P68">
-        <v>-22.74328229452378</v>
+        <v>-25.6437197510562</v>
       </c>
       <c r="Q68">
-        <v>158.4567177054763</v>
+        <v>155.5562802489438</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2379877842965911</v>
+        <v>0.2438116565480029</v>
       </c>
       <c r="T68">
-        <v>1.545483471983179</v>
+        <v>1.592316304467518</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2223072813239283</v>
+        <v>0.2189892621996906</v>
       </c>
       <c r="W68">
-        <v>0.1141652911016473</v>
+        <v>0.1146523763090854</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8811919955368936</v>
+        <v>0.8680398762005221</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1572749387879282</v>
+        <v>0.1582849387879282</v>
       </c>
       <c r="C69">
-        <v>527.8562492530016</v>
+        <v>480.9874331156045</v>
       </c>
       <c r="D69">
-        <v>2276.964249253002</v>
+        <v>2256.519433115604</v>
       </c>
       <c r="E69">
-        <v>-756.5919999999999</v>
+        <v>-730.1679999999999</v>
       </c>
       <c r="F69">
-        <v>1770.408</v>
+        <v>1796.832</v>
       </c>
       <c r="G69">
         <v>21.3</v>
@@ -6939,37 +6939,37 @@
         <v>225.6</v>
       </c>
       <c r="M69">
-        <v>259.8958944</v>
+        <v>263.7749376</v>
       </c>
       <c r="N69">
-        <v>-34.29589440000004</v>
+        <v>-38.17493760000005</v>
       </c>
       <c r="O69">
-        <v>-8.652174648943843</v>
+        <v>-9.630780392411436</v>
       </c>
       <c r="P69">
-        <v>-25.6437197510562</v>
+        <v>-28.54415720758861</v>
       </c>
       <c r="Q69">
-        <v>155.5562802489438</v>
+        <v>152.6558427924114</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2438116565480029</v>
+        <v>0.249999520815128</v>
       </c>
       <c r="T69">
-        <v>1.592316304467518</v>
+        <v>1.642076188982128</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2189892621996906</v>
+        <v>0.2157688318732245</v>
       </c>
       <c r="W69">
-        <v>0.1146523763090854</v>
+        <v>0.1151251354810107</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8680398762005221</v>
+        <v>0.8552745839034556</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1582849387879282</v>
+        <v>0.1592949387879282</v>
       </c>
       <c r="C70">
-        <v>480.9874331156045</v>
+        <v>434.4824968924895</v>
       </c>
       <c r="D70">
-        <v>2256.519433115604</v>
+        <v>2236.43849689249</v>
       </c>
       <c r="E70">
-        <v>-730.1679999999999</v>
+        <v>-703.7439999999997</v>
       </c>
       <c r="F70">
-        <v>1796.832</v>
+        <v>1823.256</v>
       </c>
       <c r="G70">
         <v>21.3</v>
@@ -7021,37 +7021,37 @@
         <v>225.6</v>
       </c>
       <c r="M70">
-        <v>263.7749376</v>
+        <v>267.6539808000001</v>
       </c>
       <c r="N70">
-        <v>-38.17493760000005</v>
+        <v>-42.05398080000006</v>
       </c>
       <c r="O70">
-        <v>-9.630780392411436</v>
+        <v>-10.60938613587903</v>
       </c>
       <c r="P70">
-        <v>-28.54415720758861</v>
+        <v>-31.44459466412103</v>
       </c>
       <c r="Q70">
-        <v>152.6558427924114</v>
+        <v>149.755405335879</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.249999520815128</v>
+        <v>0.2565866021317451</v>
       </c>
       <c r="T70">
-        <v>1.642076188982128</v>
+        <v>1.695046388626713</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2157688318732245</v>
+        <v>0.2126417473533228</v>
       </c>
       <c r="W70">
-        <v>0.1151251354810107</v>
+        <v>0.1155841914885322</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8552745839034556</v>
+        <v>0.8428793000787678</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1592949387879282</v>
+        <v>0.1603049387879282</v>
       </c>
       <c r="C71">
-        <v>434.4824968924895</v>
+        <v>388.3318116877149</v>
       </c>
       <c r="D71">
-        <v>2236.43849689249</v>
+        <v>2216.711811687715</v>
       </c>
       <c r="E71">
-        <v>-703.7439999999997</v>
+        <v>-677.3199999999997</v>
       </c>
       <c r="F71">
-        <v>1823.256</v>
+        <v>1849.68</v>
       </c>
       <c r="G71">
         <v>21.3</v>
@@ -7103,37 +7103,37 @@
         <v>225.6</v>
       </c>
       <c r="M71">
-        <v>267.6539808000001</v>
+        <v>271.5330240000001</v>
       </c>
       <c r="N71">
-        <v>-42.05398080000006</v>
+        <v>-45.93302400000007</v>
       </c>
       <c r="O71">
-        <v>-10.60938613587903</v>
+        <v>-11.58799187934662</v>
       </c>
       <c r="P71">
-        <v>-31.44459466412103</v>
+        <v>-34.34503212065345</v>
       </c>
       <c r="Q71">
-        <v>149.755405335879</v>
+        <v>146.8549678793466</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2565866021317451</v>
+        <v>0.2636128222028032</v>
       </c>
       <c r="T71">
-        <v>1.695046388626713</v>
+        <v>1.75154793491427</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2126417473533228</v>
+        <v>0.2096040081054181</v>
       </c>
       <c r="W71">
-        <v>0.1155841914885322</v>
+        <v>0.1160301316101246</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8428793000787678</v>
+        <v>0.8308381672204996</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1603049387879282</v>
+        <v>0.1613149387879282</v>
       </c>
       <c r="C72">
-        <v>388.3318116877149</v>
+        <v>342.5260853647246</v>
       </c>
       <c r="D72">
-        <v>2216.711811687715</v>
+        <v>2197.330085364725</v>
       </c>
       <c r="E72">
-        <v>-677.3199999999997</v>
+        <v>-650.8959999999997</v>
       </c>
       <c r="F72">
-        <v>1849.68</v>
+        <v>1876.104</v>
       </c>
       <c r="G72">
         <v>21.3</v>
@@ -7185,37 +7185,37 @@
         <v>225.6</v>
       </c>
       <c r="M72">
-        <v>271.5330240000001</v>
+        <v>275.4120672000001</v>
       </c>
       <c r="N72">
-        <v>-45.93302400000007</v>
+        <v>-49.81206720000009</v>
       </c>
       <c r="O72">
-        <v>-11.58799187934662</v>
+        <v>-12.56659762281422</v>
       </c>
       <c r="P72">
-        <v>-34.34503212065345</v>
+        <v>-37.24546957718587</v>
       </c>
       <c r="Q72">
-        <v>146.8549678793466</v>
+        <v>143.9545304228141</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2636128222028032</v>
+        <v>0.2711236091753138</v>
       </c>
       <c r="T72">
-        <v>1.75154793491427</v>
+        <v>1.811946139566487</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2096040081054181</v>
+        <v>0.2066518389771728</v>
       </c>
       <c r="W72">
-        <v>0.1160301316101246</v>
+        <v>0.116463510038151</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8308381672204996</v>
+        <v>0.8191362212033094</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1613149387879282</v>
+        <v>0.1623249387879282</v>
       </c>
       <c r="C73">
-        <v>342.5260853647253</v>
+        <v>297.0563479517457</v>
       </c>
       <c r="D73">
-        <v>2197.330085364725</v>
+        <v>2178.284347951746</v>
       </c>
       <c r="E73">
-        <v>-650.896</v>
+        <v>-624.472</v>
       </c>
       <c r="F73">
-        <v>1876.104</v>
+        <v>1902.528</v>
       </c>
       <c r="G73">
         <v>21.3</v>
@@ -7267,37 +7267,37 @@
         <v>225.6</v>
       </c>
       <c r="M73">
-        <v>275.4120672</v>
+        <v>279.2911104</v>
       </c>
       <c r="N73">
-        <v>-49.81206720000003</v>
+        <v>-53.69111040000004</v>
       </c>
       <c r="O73">
-        <v>-12.5665976228142</v>
+        <v>-13.54520336628179</v>
       </c>
       <c r="P73">
-        <v>-37.24546957718583</v>
+        <v>-40.14590703371825</v>
       </c>
       <c r="Q73">
-        <v>143.9545304228142</v>
+        <v>141.0540929662818</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2711236091753136</v>
+        <v>0.2791708809315749</v>
       </c>
       <c r="T73">
-        <v>1.811946139566486</v>
+        <v>1.876658501693861</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2066518389771728</v>
+        <v>0.2037816745469343</v>
       </c>
       <c r="W73">
-        <v>0.116463510038151</v>
+        <v>0.1168848501765101</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8191362212033096</v>
+        <v>0.8077593292421525</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1623249387879282</v>
+        <v>0.2057765753931675</v>
       </c>
       <c r="C74">
-        <v>297.0563479517457</v>
+        <v>-321.0168961795443</v>
       </c>
       <c r="D74">
-        <v>2178.284347951746</v>
+        <v>1586.635103820456</v>
       </c>
       <c r="E74">
-        <v>-624.472</v>
+        <v>-598.048</v>
       </c>
       <c r="F74">
-        <v>1902.528</v>
+        <v>1928.952</v>
       </c>
       <c r="G74">
         <v>21.3</v>
@@ -7349,45 +7349,45 @@
         <v>225.6</v>
       </c>
       <c r="M74">
-        <v>279.2911104</v>
+        <v>387.3335616</v>
       </c>
       <c r="N74">
-        <v>-53.69111040000004</v>
+        <v>-161.7335616</v>
       </c>
       <c r="O74">
-        <v>-13.54520336628179</v>
+        <v>-40.80217314755074</v>
       </c>
       <c r="P74">
-        <v>-40.14590703371825</v>
+        <v>-120.9313884524493</v>
       </c>
       <c r="Q74">
-        <v>141.0540929662818</v>
+        <v>60.26861154755076</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2791708809315749</v>
+        <v>0.299005493578075</v>
       </c>
       <c r="T74">
-        <v>1.876658501693861</v>
+        <v>2.036159097064938</v>
       </c>
       <c r="U74">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.2037816745469343</v>
+        <v>0.1469390102119793</v>
       </c>
       <c r="W74">
-        <v>0.1168848501765101</v>
+        <v>0.1712946467494346</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8077593292421525</v>
+        <v>0.5824437187113093</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2057765753931675</v>
+        <v>0.2073265753931675</v>
       </c>
       <c r="C75">
-        <v>-321.0168961795443</v>
+        <v>-362.6661580594275</v>
       </c>
       <c r="D75">
-        <v>1586.635103820456</v>
+        <v>1571.409841940573</v>
       </c>
       <c r="E75">
-        <v>-598.048</v>
+        <v>-571.624</v>
       </c>
       <c r="F75">
-        <v>1928.952</v>
+        <v>1955.376</v>
       </c>
       <c r="G75">
         <v>21.3</v>
@@ -7431,37 +7431,37 @@
         <v>225.6</v>
       </c>
       <c r="M75">
-        <v>387.3335616</v>
+        <v>392.6395008</v>
       </c>
       <c r="N75">
-        <v>-161.7335616</v>
+        <v>-167.0395008</v>
       </c>
       <c r="O75">
-        <v>-40.80217314755074</v>
+        <v>-42.14075648057725</v>
       </c>
       <c r="P75">
-        <v>-120.9313884524493</v>
+        <v>-124.8987443194228</v>
       </c>
       <c r="Q75">
-        <v>60.26861154755076</v>
+        <v>56.30125568057726</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.299005493578075</v>
+        <v>0.3087441664080009</v>
       </c>
       <c r="T75">
-        <v>2.036159097064938</v>
+        <v>2.114472908490512</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1469390102119793</v>
+        <v>0.1449533479118174</v>
       </c>
       <c r="W75">
-        <v>0.1712946467494346</v>
+        <v>0.171693367739307</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5824437187113093</v>
+        <v>0.574572857647643</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2073265753931675</v>
+        <v>0.2088765753931675</v>
       </c>
       <c r="C76">
-        <v>-362.6661580594275</v>
+        <v>-404.0259957119881</v>
       </c>
       <c r="D76">
-        <v>1571.409841940573</v>
+        <v>1556.474004288012</v>
       </c>
       <c r="E76">
-        <v>-571.624</v>
+        <v>-545.1999999999998</v>
       </c>
       <c r="F76">
-        <v>1955.376</v>
+        <v>1981.8</v>
       </c>
       <c r="G76">
         <v>21.3</v>
@@ -7513,37 +7513,37 @@
         <v>225.6</v>
       </c>
       <c r="M76">
-        <v>392.6395008</v>
+        <v>397.9454400000001</v>
       </c>
       <c r="N76">
-        <v>-167.0395008</v>
+        <v>-172.3454400000001</v>
       </c>
       <c r="O76">
-        <v>-42.14075648057725</v>
+        <v>-43.47933981360379</v>
       </c>
       <c r="P76">
-        <v>-124.8987443194228</v>
+        <v>-128.8661001863963</v>
       </c>
       <c r="Q76">
-        <v>56.30125568057726</v>
+        <v>52.33389981360372</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3087441664080009</v>
+        <v>0.319261933064321</v>
       </c>
       <c r="T76">
-        <v>2.114472908490512</v>
+        <v>2.199051824830133</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1449533479118174</v>
+        <v>0.1430206366063265</v>
       </c>
       <c r="W76">
-        <v>0.171693367739307</v>
+        <v>0.1720814561694496</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.574572857647643</v>
+        <v>0.566911886212341</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2088765753931675</v>
+        <v>0.2104265753931675</v>
       </c>
       <c r="C77">
-        <v>-404.0259957119881</v>
+        <v>-445.1045841396756</v>
       </c>
       <c r="D77">
-        <v>1556.474004288012</v>
+        <v>1541.819415860325</v>
       </c>
       <c r="E77">
-        <v>-545.1999999999998</v>
+        <v>-518.7759999999998</v>
       </c>
       <c r="F77">
-        <v>1981.8</v>
+        <v>2008.224</v>
       </c>
       <c r="G77">
         <v>21.3</v>
@@ -7595,37 +7595,37 @@
         <v>225.6</v>
       </c>
       <c r="M77">
-        <v>397.9454400000001</v>
+        <v>403.2513792</v>
       </c>
       <c r="N77">
-        <v>-172.3454400000001</v>
+        <v>-177.6513792</v>
       </c>
       <c r="O77">
-        <v>-43.47933981360379</v>
+        <v>-44.81792314663029</v>
       </c>
       <c r="P77">
-        <v>-128.8661001863963</v>
+        <v>-132.8334560533698</v>
       </c>
       <c r="Q77">
-        <v>52.33389981360372</v>
+        <v>48.36654394663026</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.319261933064321</v>
+        <v>0.3306561802753344</v>
       </c>
       <c r="T77">
-        <v>2.199051824830133</v>
+        <v>2.290678984198056</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1430206366063265</v>
+        <v>0.1411387861246643</v>
       </c>
       <c r="W77">
-        <v>0.1720814561694496</v>
+        <v>0.1724593317461674</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.566911886212341</v>
+        <v>0.5594525192884945</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2104265753931675</v>
+        <v>0.2119765753931675</v>
       </c>
       <c r="C78">
-        <v>-445.1045841396756</v>
+        <v>-485.9097933379589</v>
       </c>
       <c r="D78">
-        <v>1541.819415860325</v>
+        <v>1527.438206662041</v>
       </c>
       <c r="E78">
-        <v>-518.7759999999998</v>
+        <v>-492.3519999999999</v>
       </c>
       <c r="F78">
-        <v>2008.224</v>
+        <v>2034.648</v>
       </c>
       <c r="G78">
         <v>21.3</v>
@@ -7677,37 +7677,37 @@
         <v>225.6</v>
       </c>
       <c r="M78">
-        <v>403.2513792</v>
+        <v>408.5573184</v>
       </c>
       <c r="N78">
-        <v>-177.6513792</v>
+        <v>-182.9573184</v>
       </c>
       <c r="O78">
-        <v>-44.81792314663029</v>
+        <v>-46.15650647965681</v>
       </c>
       <c r="P78">
-        <v>-132.8334560533698</v>
+        <v>-136.8008119203432</v>
       </c>
       <c r="Q78">
-        <v>48.36654394663026</v>
+        <v>44.39918807965677</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3306561802753344</v>
+        <v>0.3430412315916532</v>
       </c>
       <c r="T78">
-        <v>2.290678984198056</v>
+        <v>2.390273722641449</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1411387861246643</v>
+        <v>0.139305814876292</v>
       </c>
       <c r="W78">
-        <v>0.1724593317461674</v>
+        <v>0.1728273923728406</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5594525192884945</v>
+        <v>0.5521869021548775</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2119765753931675</v>
+        <v>0.2135265753931675</v>
       </c>
       <c r="C79">
-        <v>-485.9097933379589</v>
+        <v>-526.4492023885309</v>
       </c>
       <c r="D79">
-        <v>1527.438206662041</v>
+        <v>1513.322797611469</v>
       </c>
       <c r="E79">
-        <v>-492.3519999999999</v>
+        <v>-465.9279999999999</v>
       </c>
       <c r="F79">
-        <v>2034.648</v>
+        <v>2061.072</v>
       </c>
       <c r="G79">
         <v>21.3</v>
@@ -7759,37 +7759,37 @@
         <v>225.6</v>
       </c>
       <c r="M79">
-        <v>408.5573184</v>
+        <v>413.8632576000001</v>
       </c>
       <c r="N79">
-        <v>-182.9573184</v>
+        <v>-188.2632576000001</v>
       </c>
       <c r="O79">
-        <v>-46.15650647965681</v>
+        <v>-47.49508981268332</v>
       </c>
       <c r="P79">
-        <v>-136.8008119203432</v>
+        <v>-140.7681677873167</v>
       </c>
       <c r="Q79">
-        <v>44.39918807965677</v>
+        <v>40.43183221268328</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3430412315916532</v>
+        <v>0.3565521966640012</v>
       </c>
       <c r="T79">
-        <v>2.390273722641449</v>
+        <v>2.498922528216061</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.139305814876292</v>
+        <v>0.1375198428906985</v>
       </c>
       <c r="W79">
-        <v>0.1728273923728406</v>
+        <v>0.1731860155475478</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5521869021548775</v>
+        <v>0.5451075828964818</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2135265753931675</v>
+        <v>0.2150765753931675</v>
       </c>
       <c r="C80">
-        <v>-526.4492023885309</v>
+        <v>-566.7301127782268</v>
       </c>
       <c r="D80">
-        <v>1513.322797611469</v>
+        <v>1499.465887221773</v>
       </c>
       <c r="E80">
-        <v>-465.9279999999999</v>
+        <v>-439.5039999999999</v>
       </c>
       <c r="F80">
-        <v>2061.072</v>
+        <v>2087.496</v>
       </c>
       <c r="G80">
         <v>21.3</v>
@@ -7841,37 +7841,37 @@
         <v>225.6</v>
       </c>
       <c r="M80">
-        <v>413.8632576000001</v>
+        <v>419.1691968</v>
       </c>
       <c r="N80">
-        <v>-188.2632576000001</v>
+        <v>-193.5691968</v>
       </c>
       <c r="O80">
-        <v>-47.49508981268332</v>
+        <v>-48.83367314570982</v>
       </c>
       <c r="P80">
-        <v>-140.7681677873167</v>
+        <v>-144.7355236542902</v>
       </c>
       <c r="Q80">
-        <v>40.43183221268328</v>
+        <v>36.46447634570981</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3565521966640012</v>
+        <v>0.3713499203146678</v>
       </c>
       <c r="T80">
-        <v>2.498922528216061</v>
+        <v>2.617918839083492</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1375198428906985</v>
+        <v>0.135779085385753</v>
       </c>
       <c r="W80">
-        <v>0.1731860155475478</v>
+        <v>0.1735355596545408</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5451075828964818</v>
+        <v>0.5382074869104503</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2150765753931675</v>
+        <v>0.2166265753931675</v>
       </c>
       <c r="C81">
-        <v>-566.7301127782268</v>
+        <v>-606.7595609928539</v>
       </c>
       <c r="D81">
-        <v>1499.465887221773</v>
+        <v>1485.860439007146</v>
       </c>
       <c r="E81">
-        <v>-439.5039999999999</v>
+        <v>-413.0799999999999</v>
       </c>
       <c r="F81">
-        <v>2087.496</v>
+        <v>2113.92</v>
       </c>
       <c r="G81">
         <v>21.3</v>
@@ -7923,37 +7923,37 @@
         <v>225.6</v>
       </c>
       <c r="M81">
-        <v>419.1691968</v>
+        <v>424.475136</v>
       </c>
       <c r="N81">
-        <v>-193.5691968</v>
+        <v>-198.875136</v>
       </c>
       <c r="O81">
-        <v>-48.83367314570982</v>
+        <v>-50.17225647873634</v>
       </c>
       <c r="P81">
-        <v>-144.7355236542902</v>
+        <v>-148.7028795212637</v>
       </c>
       <c r="Q81">
-        <v>36.46447634570981</v>
+        <v>32.49712047873632</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3713499203146678</v>
+        <v>0.3876274163304013</v>
       </c>
       <c r="T81">
-        <v>2.617918839083492</v>
+        <v>2.748814781037667</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.135779085385753</v>
+        <v>0.1340818468184311</v>
       </c>
       <c r="W81">
-        <v>0.1735355596545408</v>
+        <v>0.173876365158859</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5382074869104503</v>
+        <v>0.5314798933240696</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2166265753931675</v>
+        <v>0.2181765753931675</v>
       </c>
       <c r="C82">
-        <v>-606.7595609928539</v>
+        <v>-646.5443304315552</v>
       </c>
       <c r="D82">
-        <v>1485.860439007146</v>
+        <v>1472.499669568445</v>
       </c>
       <c r="E82">
-        <v>-413.0799999999999</v>
+        <v>-386.6559999999999</v>
       </c>
       <c r="F82">
-        <v>2113.92</v>
+        <v>2140.344</v>
       </c>
       <c r="G82">
         <v>21.3</v>
@@ -8005,37 +8005,37 @@
         <v>225.6</v>
       </c>
       <c r="M82">
-        <v>424.475136</v>
+        <v>429.7810752</v>
       </c>
       <c r="N82">
-        <v>-198.875136</v>
+        <v>-204.1810752</v>
       </c>
       <c r="O82">
-        <v>-50.17225647873634</v>
+        <v>-51.51083981176285</v>
       </c>
       <c r="P82">
-        <v>-148.7028795212637</v>
+        <v>-152.6702353882372</v>
       </c>
       <c r="Q82">
-        <v>32.49712047873632</v>
+        <v>28.52976461176283</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3876274163304013</v>
+        <v>0.4056183329793697</v>
       </c>
       <c r="T82">
-        <v>2.748814781037667</v>
+        <v>2.893489243197544</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1340818468184311</v>
+        <v>0.1324265153762282</v>
       </c>
       <c r="W82">
-        <v>0.173876365158859</v>
+        <v>0.1742087557124534</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5314798933240696</v>
+        <v>0.524918413159575</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2181765753931675</v>
+        <v>0.2197265753931675</v>
       </c>
       <c r="C83">
-        <v>-646.5443304315552</v>
+        <v>-686.0909626841117</v>
       </c>
       <c r="D83">
-        <v>1472.499669568445</v>
+        <v>1459.377037315888</v>
       </c>
       <c r="E83">
-        <v>-386.6559999999999</v>
+        <v>-360.232</v>
       </c>
       <c r="F83">
-        <v>2140.344</v>
+        <v>2166.768</v>
       </c>
       <c r="G83">
         <v>21.3</v>
@@ -8087,37 +8087,37 @@
         <v>225.6</v>
       </c>
       <c r="M83">
-        <v>429.7810752</v>
+        <v>435.0870144</v>
       </c>
       <c r="N83">
-        <v>-204.1810752</v>
+        <v>-209.4870144</v>
       </c>
       <c r="O83">
-        <v>-51.51083981176285</v>
+        <v>-52.84942314478937</v>
       </c>
       <c r="P83">
-        <v>-152.6702353882372</v>
+        <v>-156.6375912552107</v>
       </c>
       <c r="Q83">
-        <v>28.52976461176283</v>
+        <v>24.56240874478934</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4056183329793697</v>
+        <v>0.4256082403671125</v>
       </c>
       <c r="T83">
-        <v>2.893489243197544</v>
+        <v>3.054238645597407</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1324265153762282</v>
+        <v>0.1308115578716401</v>
       </c>
       <c r="W83">
-        <v>0.1742087557124534</v>
+        <v>0.1745330391793747</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.524918413159575</v>
+        <v>0.5185169690966533</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2197265753931675</v>
+        <v>0.2212765753931675</v>
       </c>
       <c r="C84">
-        <v>-686.0909626841117</v>
+        <v>-725.4057682105556</v>
       </c>
       <c r="D84">
-        <v>1459.377037315888</v>
+        <v>1446.486231789445</v>
       </c>
       <c r="E84">
-        <v>-360.232</v>
+        <v>-333.8079999999995</v>
       </c>
       <c r="F84">
-        <v>2166.768</v>
+        <v>2193.192</v>
       </c>
       <c r="G84">
         <v>21.3</v>
@@ -8169,37 +8169,37 @@
         <v>225.6</v>
       </c>
       <c r="M84">
-        <v>435.0870144</v>
+        <v>440.3929536000001</v>
       </c>
       <c r="N84">
-        <v>-209.4870144</v>
+        <v>-214.7929536000001</v>
       </c>
       <c r="O84">
-        <v>-52.84942314478937</v>
+        <v>-54.1880064778159</v>
       </c>
       <c r="P84">
-        <v>-156.6375912552107</v>
+        <v>-160.6049471221842</v>
       </c>
       <c r="Q84">
-        <v>24.56240874478934</v>
+        <v>20.59505287781579</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4256082403671125</v>
+        <v>0.447949901565178</v>
       </c>
       <c r="T84">
-        <v>3.054238645597407</v>
+        <v>3.233899742397255</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1308115578716401</v>
+        <v>0.1292355150057167</v>
       </c>
       <c r="W84">
-        <v>0.1745330391793747</v>
+        <v>0.1748495085868521</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5185169690966533</v>
+        <v>0.5122697766978984</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2212765753931675</v>
+        <v>0.2228265753931675</v>
       </c>
       <c r="C85">
-        <v>-725.4057682105556</v>
+        <v>-764.494836459739</v>
       </c>
       <c r="D85">
-        <v>1446.486231789445</v>
+        <v>1433.821163540262</v>
       </c>
       <c r="E85">
-        <v>-333.8079999999995</v>
+        <v>-307.3839999999996</v>
       </c>
       <c r="F85">
-        <v>2193.192</v>
+        <v>2219.616</v>
       </c>
       <c r="G85">
         <v>21.3</v>
@@ -8251,37 +8251,37 @@
         <v>225.6</v>
       </c>
       <c r="M85">
-        <v>440.3929536000001</v>
+        <v>445.6988928000001</v>
       </c>
       <c r="N85">
-        <v>-214.7929536000001</v>
+        <v>-220.0988928000001</v>
       </c>
       <c r="O85">
-        <v>-54.1880064778159</v>
+        <v>-55.52658981084242</v>
       </c>
       <c r="P85">
-        <v>-160.6049471221842</v>
+        <v>-164.5723029891577</v>
       </c>
       <c r="Q85">
-        <v>20.59505287781579</v>
+        <v>16.6276970108423</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.447949901565178</v>
+        <v>0.4730842704130017</v>
       </c>
       <c r="T85">
-        <v>3.233899742397255</v>
+        <v>3.436018476297084</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1292355150057167</v>
+        <v>0.1276969969699344</v>
       </c>
       <c r="W85">
-        <v>0.1748495085868521</v>
+        <v>0.1751584430084372</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5122697766978984</v>
+        <v>0.5061713269753043</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2228265753931675</v>
+        <v>0.2243765753931675</v>
       </c>
       <c r="C86">
-        <v>-764.4948364597385</v>
+        <v>-803.3640454609433</v>
       </c>
       <c r="D86">
-        <v>1433.821163540262</v>
+        <v>1421.375954539057</v>
       </c>
       <c r="E86">
-        <v>-307.384</v>
+        <v>-280.96</v>
       </c>
       <c r="F86">
-        <v>2219.616</v>
+        <v>2246.04</v>
       </c>
       <c r="G86">
         <v>21.3</v>
@@ -8333,37 +8333,37 @@
         <v>225.6</v>
       </c>
       <c r="M86">
-        <v>445.6988928</v>
+        <v>451.004832</v>
       </c>
       <c r="N86">
-        <v>-220.0988928</v>
+        <v>-225.404832</v>
       </c>
       <c r="O86">
-        <v>-55.52658981084239</v>
+        <v>-56.8651731438689</v>
       </c>
       <c r="P86">
-        <v>-164.5723029891576</v>
+        <v>-168.5396588561311</v>
       </c>
       <c r="Q86">
-        <v>16.62769701084238</v>
+        <v>12.66034114386889</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4730842704130014</v>
+        <v>0.5015698884405349</v>
       </c>
       <c r="T86">
-        <v>3.436018476297082</v>
+        <v>3.665086374716888</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1276969969699344</v>
+        <v>0.1261946793585234</v>
       </c>
       <c r="W86">
-        <v>0.1751584430084372</v>
+        <v>0.1754601083848085</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5061713269753045</v>
+        <v>0.5002163701873596</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2243765753931675</v>
+        <v>0.2572458422607042</v>
       </c>
       <c r="C87">
-        <v>-803.3640454609433</v>
+        <v>-1050.741009441388</v>
       </c>
       <c r="D87">
-        <v>1421.375954539057</v>
+        <v>1200.422990558612</v>
       </c>
       <c r="E87">
-        <v>-280.96</v>
+        <v>-254.5360000000001</v>
       </c>
       <c r="F87">
-        <v>2246.04</v>
+        <v>2272.464</v>
       </c>
       <c r="G87">
         <v>21.3</v>
@@ -8415,45 +8415,45 @@
         <v>225.6</v>
       </c>
       <c r="M87">
-        <v>451.004832</v>
+        <v>535.8470112</v>
       </c>
       <c r="N87">
-        <v>-225.404832</v>
+        <v>-310.2470112</v>
       </c>
       <c r="O87">
-        <v>-56.8651731438689</v>
+        <v>-78.26917396897611</v>
       </c>
       <c r="P87">
-        <v>-168.5396588561311</v>
+        <v>-231.9778372310239</v>
       </c>
       <c r="Q87">
-        <v>12.66034114386889</v>
+        <v>-50.77783723102385</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5015698884405349</v>
+        <v>0.5428339295258359</v>
       </c>
       <c r="T87">
-        <v>3.665086374716888</v>
+        <v>3.996912321501055</v>
       </c>
       <c r="U87">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1261946793585234</v>
+        <v>0.1062139173566127</v>
       </c>
       <c r="W87">
-        <v>0.1754601083848085</v>
+        <v>0.2107547582873107</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.5002163701873596</v>
+        <v>0.4210156915773052</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2572458422607042</v>
+        <v>0.2591458422607043</v>
       </c>
       <c r="C88">
-        <v>-1050.741009441388</v>
+        <v>-1087.855649848967</v>
       </c>
       <c r="D88">
-        <v>1200.422990558612</v>
+        <v>1189.732350151033</v>
       </c>
       <c r="E88">
-        <v>-254.5360000000001</v>
+        <v>-228.1120000000001</v>
       </c>
       <c r="F88">
-        <v>2272.464</v>
+        <v>2298.888</v>
       </c>
       <c r="G88">
         <v>21.3</v>
@@ -8497,37 +8497,37 @@
         <v>225.6</v>
       </c>
       <c r="M88">
-        <v>535.8470112</v>
+        <v>542.0777904</v>
       </c>
       <c r="N88">
-        <v>-310.2470112</v>
+        <v>-316.4777904</v>
       </c>
       <c r="O88">
-        <v>-78.26917396897611</v>
+        <v>-79.84107611005007</v>
       </c>
       <c r="P88">
-        <v>-231.9778372310239</v>
+        <v>-236.6367142899499</v>
       </c>
       <c r="Q88">
-        <v>-50.77783723102385</v>
+        <v>-55.43671428994992</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5428339295258359</v>
+        <v>0.5810673087201309</v>
       </c>
       <c r="T88">
-        <v>3.996912321501055</v>
+        <v>4.304367115462674</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1062139173566127</v>
+        <v>0.104993067731824</v>
       </c>
       <c r="W88">
-        <v>0.2107547582873107</v>
+        <v>0.2110426346288359</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4210156915773052</v>
+        <v>0.4161764307545776</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2591458422607043</v>
+        <v>0.2610458422607043</v>
       </c>
       <c r="C89">
-        <v>-1087.855649848967</v>
+        <v>-1124.781555212366</v>
       </c>
       <c r="D89">
-        <v>1189.732350151033</v>
+        <v>1179.230444787634</v>
       </c>
       <c r="E89">
-        <v>-228.1120000000001</v>
+        <v>-201.6880000000001</v>
       </c>
       <c r="F89">
-        <v>2298.888</v>
+        <v>2325.312</v>
       </c>
       <c r="G89">
         <v>21.3</v>
@@ -8579,37 +8579,37 @@
         <v>225.6</v>
       </c>
       <c r="M89">
-        <v>542.0777904</v>
+        <v>548.3085695999999</v>
       </c>
       <c r="N89">
-        <v>-316.4777904</v>
+        <v>-322.7085695999999</v>
       </c>
       <c r="O89">
-        <v>-79.84107611005007</v>
+        <v>-81.41297825112402</v>
       </c>
       <c r="P89">
-        <v>-236.6367142899499</v>
+        <v>-241.2955913488759</v>
       </c>
       <c r="Q89">
-        <v>-55.43671428994992</v>
+        <v>-60.0955913488759</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5810673087201309</v>
+        <v>0.6256729177801418</v>
       </c>
       <c r="T89">
-        <v>4.304367115462674</v>
+        <v>4.663064375084564</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.104993067731824</v>
+        <v>0.1037999646894169</v>
       </c>
       <c r="W89">
-        <v>0.2110426346288359</v>
+        <v>0.2113239683262355</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4161764307545776</v>
+        <v>0.4114471531323666</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2610458422607043</v>
+        <v>0.2629458422607043</v>
       </c>
       <c r="C90">
-        <v>-1124.781555212366</v>
+        <v>-1161.523679758387</v>
       </c>
       <c r="D90">
-        <v>1179.230444787634</v>
+        <v>1168.912320241614</v>
       </c>
       <c r="E90">
-        <v>-201.6880000000001</v>
+        <v>-175.2639999999997</v>
       </c>
       <c r="F90">
-        <v>2325.312</v>
+        <v>2351.736</v>
       </c>
       <c r="G90">
         <v>21.3</v>
@@ -8661,37 +8661,37 @@
         <v>225.6</v>
       </c>
       <c r="M90">
-        <v>548.3085695999999</v>
+        <v>554.5393488000001</v>
       </c>
       <c r="N90">
-        <v>-322.7085695999999</v>
+        <v>-328.9393488000001</v>
       </c>
       <c r="O90">
-        <v>-81.41297825112402</v>
+        <v>-82.98488039219801</v>
       </c>
       <c r="P90">
-        <v>-241.2955913488759</v>
+        <v>-245.954468407802</v>
       </c>
       <c r="Q90">
-        <v>-60.0955913488759</v>
+        <v>-64.75446840780202</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6256729177801418</v>
+        <v>0.6783886375783366</v>
       </c>
       <c r="T90">
-        <v>4.663064375084564</v>
+        <v>5.08697931827407</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1037999646894169</v>
+        <v>0.1026336729513336</v>
       </c>
       <c r="W90">
-        <v>0.2113239683262355</v>
+        <v>0.2115989799180756</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4114471531323666</v>
+        <v>0.4068241514117781</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2629458422607043</v>
+        <v>0.2648458422607043</v>
       </c>
       <c r="C91">
-        <v>-1161.523679758387</v>
+        <v>-1198.086805822308</v>
       </c>
       <c r="D91">
-        <v>1168.912320241614</v>
+        <v>1158.773194177692</v>
       </c>
       <c r="E91">
-        <v>-175.2639999999997</v>
+        <v>-148.8399999999997</v>
       </c>
       <c r="F91">
-        <v>2351.736</v>
+        <v>2378.16</v>
       </c>
       <c r="G91">
         <v>21.3</v>
@@ -8743,37 +8743,37 @@
         <v>225.6</v>
       </c>
       <c r="M91">
-        <v>554.5393488000001</v>
+        <v>560.7701280000001</v>
       </c>
       <c r="N91">
-        <v>-328.9393488000001</v>
+        <v>-335.1701280000001</v>
       </c>
       <c r="O91">
-        <v>-82.98488039219801</v>
+        <v>-84.55678253327198</v>
       </c>
       <c r="P91">
-        <v>-245.954468407802</v>
+        <v>-250.6133454667281</v>
       </c>
       <c r="Q91">
-        <v>-64.75446840780202</v>
+        <v>-69.41334546672809</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6783886375783366</v>
+        <v>0.7416475013361703</v>
       </c>
       <c r="T91">
-        <v>5.08697931827407</v>
+        <v>5.595677250101478</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1026336729513336</v>
+        <v>0.1014932988074299</v>
       </c>
       <c r="W91">
-        <v>0.2115989799180756</v>
+        <v>0.2118678801412081</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4068241514117781</v>
+        <v>0.4023038830627582</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2648458422607043</v>
+        <v>0.2667458422607043</v>
       </c>
       <c r="C92">
-        <v>-1198.086805822308</v>
+        <v>-1234.475551238697</v>
       </c>
       <c r="D92">
-        <v>1158.773194177692</v>
+        <v>1148.808448761303</v>
       </c>
       <c r="E92">
-        <v>-148.8399999999997</v>
+        <v>-122.4159999999997</v>
       </c>
       <c r="F92">
-        <v>2378.16</v>
+        <v>2404.584</v>
       </c>
       <c r="G92">
         <v>21.3</v>
@@ -8825,37 +8825,37 @@
         <v>225.6</v>
       </c>
       <c r="M92">
-        <v>560.7701280000001</v>
+        <v>567.0009072000001</v>
       </c>
       <c r="N92">
-        <v>-335.1701280000001</v>
+        <v>-341.4009072000001</v>
       </c>
       <c r="O92">
-        <v>-84.55678253327198</v>
+        <v>-86.12868467434595</v>
       </c>
       <c r="P92">
-        <v>-250.6133454667281</v>
+        <v>-255.2722225256542</v>
       </c>
       <c r="Q92">
-        <v>-69.41334546672809</v>
+        <v>-74.07222252565415</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7416475013361703</v>
+        <v>0.8189638903735227</v>
       </c>
       <c r="T92">
-        <v>5.595677250101478</v>
+        <v>6.21741916677942</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1014932988074299</v>
+        <v>0.100377987831524</v>
       </c>
       <c r="W92">
-        <v>0.2118678801412081</v>
+        <v>0.2121308704693266</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4023038830627582</v>
+        <v>0.3978829612708598</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2667458422607043</v>
+        <v>0.2686458422607043</v>
       </c>
       <c r="C93">
-        <v>-1234.475551238697</v>
+        <v>-1270.694376354137</v>
       </c>
       <c r="D93">
-        <v>1148.808448761303</v>
+        <v>1139.013623645863</v>
       </c>
       <c r="E93">
-        <v>-122.4159999999997</v>
+        <v>-95.99199999999973</v>
       </c>
       <c r="F93">
-        <v>2404.584</v>
+        <v>2431.008</v>
       </c>
       <c r="G93">
         <v>21.3</v>
@@ -8907,37 +8907,37 @@
         <v>225.6</v>
       </c>
       <c r="M93">
-        <v>567.0009072000001</v>
+        <v>573.2316864000001</v>
       </c>
       <c r="N93">
-        <v>-341.4009072000001</v>
+        <v>-347.6316864</v>
       </c>
       <c r="O93">
-        <v>-86.12868467434595</v>
+        <v>-87.7005868154199</v>
       </c>
       <c r="P93">
-        <v>-255.2722225256542</v>
+        <v>-259.9310995845801</v>
       </c>
       <c r="Q93">
-        <v>-74.07222252565415</v>
+        <v>-78.73109958458011</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8189638903735227</v>
+        <v>0.9156093766702132</v>
       </c>
       <c r="T93">
-        <v>6.21741916677942</v>
+        <v>6.99459656262685</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.100377987831524</v>
+        <v>0.0992869227463988</v>
       </c>
       <c r="W93">
-        <v>0.2121308704693266</v>
+        <v>0.2123881436163992</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3978829612708598</v>
+        <v>0.3935581464744374</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2686458422607043</v>
+        <v>0.2705458422607043</v>
       </c>
       <c r="C94">
-        <v>-1270.694376354137</v>
+        <v>-1306.747590684237</v>
       </c>
       <c r="D94">
-        <v>1139.013623645863</v>
+        <v>1129.384409315764</v>
       </c>
       <c r="E94">
-        <v>-95.99199999999973</v>
+        <v>-69.56799999999976</v>
       </c>
       <c r="F94">
-        <v>2431.008</v>
+        <v>2457.432</v>
       </c>
       <c r="G94">
         <v>21.3</v>
@@ -8989,37 +8989,37 @@
         <v>225.6</v>
       </c>
       <c r="M94">
-        <v>573.2316864000001</v>
+        <v>579.4624656000001</v>
       </c>
       <c r="N94">
-        <v>-347.6316864</v>
+        <v>-353.8624656000001</v>
       </c>
       <c r="O94">
-        <v>-87.7005868154199</v>
+        <v>-89.27248895649386</v>
       </c>
       <c r="P94">
-        <v>-259.9310995845801</v>
+        <v>-264.5899766435062</v>
       </c>
       <c r="Q94">
-        <v>-78.73109958458011</v>
+        <v>-83.38997664350617</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9156093766702132</v>
+        <v>1.039867859051672</v>
       </c>
       <c r="T94">
-        <v>6.99459656262685</v>
+        <v>7.993824643002115</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0992869227463988</v>
+        <v>0.09821932142654505</v>
       </c>
       <c r="W94">
-        <v>0.2123881436163992</v>
+        <v>0.2126398840076207</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3935581464744374</v>
+        <v>0.3893263384478306</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2705458422607043</v>
+        <v>0.2724458422607043</v>
       </c>
       <c r="C95">
-        <v>-1306.747590684237</v>
+        <v>-1342.639359235807</v>
       </c>
       <c r="D95">
-        <v>1129.384409315764</v>
+        <v>1119.916640764194</v>
       </c>
       <c r="E95">
-        <v>-69.56799999999976</v>
+        <v>-43.14399999999978</v>
       </c>
       <c r="F95">
-        <v>2457.432</v>
+        <v>2483.856</v>
       </c>
       <c r="G95">
         <v>21.3</v>
@@ -9071,37 +9071,37 @@
         <v>225.6</v>
       </c>
       <c r="M95">
-        <v>579.4624656000001</v>
+        <v>585.6932448000001</v>
       </c>
       <c r="N95">
-        <v>-353.8624656000001</v>
+        <v>-360.0932448000001</v>
       </c>
       <c r="O95">
-        <v>-89.27248895649386</v>
+        <v>-90.84439109756784</v>
       </c>
       <c r="P95">
-        <v>-264.5899766435062</v>
+        <v>-269.2488537024323</v>
       </c>
       <c r="Q95">
-        <v>-83.38997664350617</v>
+        <v>-88.04885370243224</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.039867859051672</v>
+        <v>1.205545835560285</v>
       </c>
       <c r="T95">
-        <v>7.993824643002115</v>
+        <v>9.326128750169136</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09821932142654505</v>
+        <v>0.09717443502839031</v>
       </c>
       <c r="W95">
-        <v>0.2126398840076207</v>
+        <v>0.2128862682203056</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3893263384478306</v>
+        <v>0.385184568889875</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2724458422607043</v>
+        <v>0.2743458422607043</v>
       </c>
       <c r="C96">
-        <v>-1342.639359235807</v>
+        <v>-1378.373708513676</v>
       </c>
       <c r="D96">
-        <v>1119.916640764194</v>
+        <v>1110.606291486324</v>
       </c>
       <c r="E96">
-        <v>-43.14399999999978</v>
+        <v>-16.7199999999998</v>
       </c>
       <c r="F96">
-        <v>2483.856</v>
+        <v>2510.28</v>
       </c>
       <c r="G96">
         <v>21.3</v>
@@ -9153,37 +9153,37 @@
         <v>225.6</v>
       </c>
       <c r="M96">
-        <v>585.6932448000001</v>
+        <v>591.924024</v>
       </c>
       <c r="N96">
-        <v>-360.0932448000001</v>
+        <v>-366.324024</v>
       </c>
       <c r="O96">
-        <v>-90.84439109756784</v>
+        <v>-92.41629323864177</v>
       </c>
       <c r="P96">
-        <v>-269.2488537024323</v>
+        <v>-273.9077307613583</v>
       </c>
       <c r="Q96">
-        <v>-88.04885370243224</v>
+        <v>-92.70773076135825</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.205545835560285</v>
+        <v>1.437495002672343</v>
       </c>
       <c r="T96">
-        <v>9.326128750169136</v>
+        <v>11.19135450020297</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09717443502839031</v>
+        <v>0.09615154623861778</v>
       </c>
       <c r="W96">
-        <v>0.2128862682203056</v>
+        <v>0.2131274653969339</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.385184568889875</v>
+        <v>0.3811299944805079</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2743458422607043</v>
+        <v>0.2762458422607043</v>
       </c>
       <c r="C97">
-        <v>-1378.373708513676</v>
+        <v>-1413.95453223036</v>
       </c>
       <c r="D97">
-        <v>1110.606291486324</v>
+        <v>1101.44946776964</v>
       </c>
       <c r="E97">
-        <v>-16.7199999999998</v>
+        <v>9.704000000000178</v>
       </c>
       <c r="F97">
-        <v>2510.28</v>
+        <v>2536.704</v>
       </c>
       <c r="G97">
         <v>21.3</v>
@@ -9235,37 +9235,37 @@
         <v>225.6</v>
       </c>
       <c r="M97">
-        <v>591.924024</v>
+        <v>598.1548032000001</v>
       </c>
       <c r="N97">
-        <v>-366.324024</v>
+        <v>-372.5548032</v>
       </c>
       <c r="O97">
-        <v>-92.41629323864177</v>
+        <v>-93.98819537971575</v>
       </c>
       <c r="P97">
-        <v>-273.9077307613583</v>
+        <v>-278.5666078202843</v>
       </c>
       <c r="Q97">
-        <v>-92.70773076135825</v>
+        <v>-97.36660782028426</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.437495002672343</v>
+        <v>1.785418753340429</v>
       </c>
       <c r="T97">
-        <v>11.19135450020297</v>
+        <v>13.98919312525372</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09615154623861778</v>
+        <v>0.09514996763196551</v>
       </c>
       <c r="W97">
-        <v>0.2131274653969339</v>
+        <v>0.2133636376323826</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3811299944805079</v>
+        <v>0.3771598903713359</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2762458422607043</v>
+        <v>0.2781458422607043</v>
       </c>
       <c r="C98">
-        <v>-1413.95453223036</v>
+        <v>-1449.385596735582</v>
       </c>
       <c r="D98">
-        <v>1101.449467769641</v>
+        <v>1092.442403264419</v>
       </c>
       <c r="E98">
-        <v>9.704000000000178</v>
+        <v>36.12800000000016</v>
       </c>
       <c r="F98">
-        <v>2536.704</v>
+        <v>2563.128</v>
       </c>
       <c r="G98">
         <v>21.3</v>
@@ -9317,37 +9317,37 @@
         <v>225.6</v>
       </c>
       <c r="M98">
-        <v>598.1548032000001</v>
+        <v>604.3855824000001</v>
       </c>
       <c r="N98">
-        <v>-372.5548032</v>
+        <v>-378.7855824000001</v>
       </c>
       <c r="O98">
-        <v>-93.98819537971575</v>
+        <v>-95.56009752078971</v>
       </c>
       <c r="P98">
-        <v>-278.5666078202843</v>
+        <v>-283.2254848792103</v>
       </c>
       <c r="Q98">
-        <v>-97.36660782028426</v>
+        <v>-102.0254848792103</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.785418753340424</v>
+        <v>2.365291671120566</v>
       </c>
       <c r="T98">
-        <v>13.98919312525368</v>
+        <v>18.65225750033824</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09514996763196551</v>
+        <v>0.09416904013060504</v>
       </c>
       <c r="W98">
-        <v>0.2133636376323826</v>
+        <v>0.2135949403372034</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3771598903713359</v>
+        <v>0.3732716440788478</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2781458422607043</v>
+        <v>0.2800458422607042</v>
       </c>
       <c r="C99">
-        <v>-1449.385596735582</v>
+        <v>-1484.670546181559</v>
       </c>
       <c r="D99">
-        <v>1092.442403264419</v>
+        <v>1083.581453818442</v>
       </c>
       <c r="E99">
-        <v>36.12800000000016</v>
+        <v>62.55200000000013</v>
       </c>
       <c r="F99">
-        <v>2563.128</v>
+        <v>2589.552</v>
       </c>
       <c r="G99">
         <v>21.3</v>
@@ -9399,37 +9399,37 @@
         <v>225.6</v>
       </c>
       <c r="M99">
-        <v>604.3855824000001</v>
+        <v>610.6163616</v>
       </c>
       <c r="N99">
-        <v>-378.7855824000001</v>
+        <v>-385.0163616</v>
       </c>
       <c r="O99">
-        <v>-95.56009752078971</v>
+        <v>-97.13199966186366</v>
       </c>
       <c r="P99">
-        <v>-283.2254848792103</v>
+        <v>-287.8843619381363</v>
       </c>
       <c r="Q99">
-        <v>-102.0254848792103</v>
+        <v>-106.6843619381363</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.365291671120566</v>
+        <v>3.525037506680848</v>
       </c>
       <c r="T99">
-        <v>18.65225750033824</v>
+        <v>27.97838625050736</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09416904013060504</v>
+        <v>0.09320813155784378</v>
       </c>
       <c r="W99">
-        <v>0.2135949403372034</v>
+        <v>0.2138215225786604</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3732716440788478</v>
+        <v>0.3694627497515127</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2800458422607042</v>
+        <v>0.2819458422607043</v>
       </c>
       <c r="C100">
-        <v>-1484.670546181559</v>
+        <v>-1519.81290743893</v>
       </c>
       <c r="D100">
-        <v>1083.581453818442</v>
+        <v>1074.86309256107</v>
       </c>
       <c r="E100">
-        <v>62.55200000000013</v>
+        <v>88.97600000000011</v>
       </c>
       <c r="F100">
-        <v>2589.552</v>
+        <v>2615.976</v>
       </c>
       <c r="G100">
         <v>21.3</v>
@@ -9481,37 +9481,37 @@
         <v>225.6</v>
       </c>
       <c r="M100">
-        <v>610.6163616</v>
+        <v>616.8471408</v>
       </c>
       <c r="N100">
-        <v>-385.0163616</v>
+        <v>-391.2471408</v>
       </c>
       <c r="O100">
-        <v>-97.13199966186366</v>
+        <v>-98.70390180293762</v>
       </c>
       <c r="P100">
-        <v>-287.8843619381363</v>
+        <v>-292.5432389970624</v>
       </c>
       <c r="Q100">
-        <v>-106.6843619381363</v>
+        <v>-111.3432389970624</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.525037506680848</v>
+        <v>7.004275013361696</v>
       </c>
       <c r="T100">
-        <v>27.97838625050736</v>
+        <v>55.95677250101471</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09320813155784378</v>
+        <v>0.09226663527948172</v>
       </c>
       <c r="W100">
-        <v>0.2138215225786604</v>
+        <v>0.2140435274010982</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3694627497515127</v>
+        <v>0.3657308027843258</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2819458422607043</v>
-      </c>
-      <c r="C101">
-        <v>-1519.81290743893</v>
-      </c>
-      <c r="D101">
-        <v>1074.86309256107</v>
-      </c>
-      <c r="E101">
-        <v>88.97600000000011</v>
-      </c>
-      <c r="F101">
-        <v>2615.976</v>
-      </c>
-      <c r="G101">
-        <v>21.3</v>
-      </c>
-      <c r="H101">
-        <v>115.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>406.8</v>
-      </c>
-      <c r="K101">
-        <v>181.2</v>
-      </c>
-      <c r="L101">
-        <v>225.6</v>
-      </c>
-      <c r="M101">
-        <v>616.8471408</v>
-      </c>
-      <c r="N101">
-        <v>-391.2471408</v>
-      </c>
-      <c r="O101">
-        <v>-98.70390180293762</v>
-      </c>
-      <c r="P101">
-        <v>-292.5432389970624</v>
-      </c>
-      <c r="Q101">
-        <v>-111.3432389970624</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.004275013361696</v>
-      </c>
-      <c r="T101">
-        <v>55.95677250101471</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09226663527948172</v>
-      </c>
-      <c r="W101">
-        <v>0.2140435274010982</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3657308027843258</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
